--- a/JBR.xlsx
+++ b/JBR.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="762">
   <si>
     <t>CODE</t>
   </si>
@@ -2302,6 +2302,9 @@
   </si>
   <si>
     <t>MANAKIB TRAVEL</t>
+  </si>
+  <si>
+    <t>AUXILLIAIRE</t>
   </si>
 </sst>
 </file>
@@ -6689,8 +6692,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>761</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -16509,7 +16515,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B889 B892:B1048576">
+  <conditionalFormatting sqref="B2:B889 A1 B892:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/JBR.xlsx
+++ b/JBR.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="767">
   <si>
     <t>CODE</t>
   </si>
@@ -2305,6 +2305,21 @@
   </si>
   <si>
     <t>AUXILLIAIRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165ND013      </t>
+  </si>
+  <si>
+    <t>BILLETIX ALGERIE TRAVEL</t>
+  </si>
+  <si>
+    <t>SARL BILLETIX ALGERIE TRAVEL</t>
+  </si>
+  <si>
+    <t>LEJDAR TRAVEL</t>
+  </si>
+  <si>
+    <t>NAMLATIC</t>
   </si>
 </sst>
 </file>
@@ -2346,7 +2361,37 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6677,7 +6722,7 @@
     <sortCondition ref="B2"/>
   </sortState>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6685,9 +6730,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C893"/>
+  <dimension ref="A1:E899"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10915,180 +10961,192 @@
         <v>514</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A385">
-        <v>411</v>
-      </c>
-      <c r="B385">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>755</v>
+      </c>
+      <c r="B385" t="s">
+        <v>762</v>
+      </c>
+      <c r="C385" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>755</v>
+      </c>
+      <c r="B386">
+        <v>1650377</v>
+      </c>
+      <c r="C386" t="s">
+        <v>765</v>
+      </c>
+      <c r="D386" t="s">
+        <v>0</v>
+      </c>
+      <c r="E386" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>755</v>
+      </c>
+      <c r="B387">
+        <v>1650378</v>
+      </c>
+      <c r="C387" t="s">
+        <v>766</v>
+      </c>
+      <c r="D387">
+        <v>1650377</v>
+      </c>
+      <c r="E387" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A388">
+        <v>411</v>
+      </c>
+      <c r="B388">
         <v>4110000</v>
       </c>
-      <c r="C385" t="s">
+      <c r="C388" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A386">
-        <v>411</v>
-      </c>
-      <c r="B386">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A389">
+        <v>411</v>
+      </c>
+      <c r="B389">
         <v>41100000</v>
       </c>
-      <c r="C386" t="s">
+      <c r="C389" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A387">
-        <v>411</v>
-      </c>
-      <c r="B387">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A390">
+        <v>411</v>
+      </c>
+      <c r="B390">
         <v>41100001</v>
       </c>
-      <c r="C387" t="s">
+      <c r="C390" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A388">
-        <v>411</v>
-      </c>
-      <c r="B388">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A391">
+        <v>411</v>
+      </c>
+      <c r="B391">
         <v>41100002</v>
       </c>
-      <c r="C388" t="s">
+      <c r="C391" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A389">
-        <v>411</v>
-      </c>
-      <c r="B389">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A392">
+        <v>411</v>
+      </c>
+      <c r="B392">
         <v>41100003</v>
       </c>
-      <c r="C389" t="s">
+      <c r="C392" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A390">
-        <v>411</v>
-      </c>
-      <c r="B390">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A393">
+        <v>411</v>
+      </c>
+      <c r="B393">
         <v>41100004</v>
       </c>
-      <c r="C390" t="s">
+      <c r="C393" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A391">
-        <v>411</v>
-      </c>
-      <c r="B391">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A394">
+        <v>411</v>
+      </c>
+      <c r="B394">
         <v>41100010</v>
       </c>
-      <c r="C391" t="s">
+      <c r="C394" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A392">
-        <v>411</v>
-      </c>
-      <c r="B392">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A395">
+        <v>411</v>
+      </c>
+      <c r="B395">
         <v>4110002</v>
       </c>
-      <c r="C392" t="s">
+      <c r="C395" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A393">
-        <v>411</v>
-      </c>
-      <c r="B393">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A396">
+        <v>411</v>
+      </c>
+      <c r="B396">
         <v>411000497</v>
       </c>
-      <c r="C393" t="s">
+      <c r="C396" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A394">
-        <v>411</v>
-      </c>
-      <c r="B394">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A397">
+        <v>411</v>
+      </c>
+      <c r="B397">
         <v>4110005</v>
       </c>
-      <c r="C394" t="s">
+      <c r="C397" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A395">
-        <v>411</v>
-      </c>
-      <c r="B395">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A398">
+        <v>411</v>
+      </c>
+      <c r="B398">
         <v>41100096</v>
       </c>
-      <c r="C395" t="s">
+      <c r="C398" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A396">
-        <v>411</v>
-      </c>
-      <c r="B396">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A399">
+        <v>411</v>
+      </c>
+      <c r="B399">
         <v>41100097</v>
       </c>
-      <c r="C396" t="s">
+      <c r="C399" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A397">
-        <v>411</v>
-      </c>
-      <c r="B397">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A400">
+        <v>411</v>
+      </c>
+      <c r="B400">
         <v>41100098</v>
       </c>
-      <c r="C397" t="s">
+      <c r="C400" t="s">
         <v>171</v>
-      </c>
-    </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A398">
-        <v>411</v>
-      </c>
-      <c r="B398">
-        <v>41100099</v>
-      </c>
-      <c r="C398" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A399">
-        <v>411</v>
-      </c>
-      <c r="B399">
-        <v>411001</v>
-      </c>
-      <c r="C399" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A400">
-        <v>411</v>
-      </c>
-      <c r="B400">
-        <v>41100100</v>
-      </c>
-      <c r="C400" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -11096,10 +11154,10 @@
         <v>411</v>
       </c>
       <c r="B401">
-        <v>41100101</v>
+        <v>41100099</v>
       </c>
       <c r="C401" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -11107,10 +11165,10 @@
         <v>411</v>
       </c>
       <c r="B402">
-        <v>41100102</v>
+        <v>411001</v>
       </c>
       <c r="C402" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -11118,10 +11176,10 @@
         <v>411</v>
       </c>
       <c r="B403">
-        <v>41100103</v>
+        <v>41100100</v>
       </c>
       <c r="C403" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
@@ -11129,10 +11187,10 @@
         <v>411</v>
       </c>
       <c r="B404">
-        <v>41100104</v>
+        <v>41100101</v>
       </c>
       <c r="C404" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
@@ -11140,10 +11198,10 @@
         <v>411</v>
       </c>
       <c r="B405">
-        <v>411001040</v>
+        <v>41100102</v>
       </c>
       <c r="C405" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -11151,10 +11209,10 @@
         <v>411</v>
       </c>
       <c r="B406">
-        <v>41100105</v>
+        <v>41100103</v>
       </c>
       <c r="C406" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -11162,10 +11220,10 @@
         <v>411</v>
       </c>
       <c r="B407">
-        <v>41100106</v>
+        <v>41100104</v>
       </c>
       <c r="C407" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -11173,10 +11231,10 @@
         <v>411</v>
       </c>
       <c r="B408">
-        <v>41100107</v>
+        <v>411001040</v>
       </c>
       <c r="C408" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -11184,10 +11242,10 @@
         <v>411</v>
       </c>
       <c r="B409">
-        <v>41100108</v>
+        <v>41100105</v>
       </c>
       <c r="C409" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -11195,10 +11253,10 @@
         <v>411</v>
       </c>
       <c r="B410">
-        <v>41100109</v>
+        <v>41100106</v>
       </c>
       <c r="C410" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -11206,10 +11264,10 @@
         <v>411</v>
       </c>
       <c r="B411">
-        <v>4110011</v>
+        <v>41100107</v>
       </c>
       <c r="C411" t="s">
-        <v>35</v>
+        <v>181</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
@@ -11217,10 +11275,10 @@
         <v>411</v>
       </c>
       <c r="B412">
-        <v>41100110</v>
+        <v>41100108</v>
       </c>
       <c r="C412" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -11228,10 +11286,10 @@
         <v>411</v>
       </c>
       <c r="B413">
-        <v>41100111</v>
+        <v>41100109</v>
       </c>
       <c r="C413" t="s">
-        <v>8</v>
+        <v>183</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -11239,10 +11297,10 @@
         <v>411</v>
       </c>
       <c r="B414">
-        <v>41100112</v>
+        <v>4110011</v>
       </c>
       <c r="C414" t="s">
-        <v>185</v>
+        <v>35</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -11250,10 +11308,10 @@
         <v>411</v>
       </c>
       <c r="B415">
-        <v>411001120</v>
+        <v>41100110</v>
       </c>
       <c r="C415" t="s">
-        <v>746</v>
+        <v>184</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -11261,10 +11319,10 @@
         <v>411</v>
       </c>
       <c r="B416">
-        <v>41100113</v>
+        <v>41100111</v>
       </c>
       <c r="C416" t="s">
-        <v>186</v>
+        <v>8</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -11272,10 +11330,10 @@
         <v>411</v>
       </c>
       <c r="B417">
-        <v>41100114</v>
+        <v>41100112</v>
       </c>
       <c r="C417" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
@@ -11283,10 +11341,10 @@
         <v>411</v>
       </c>
       <c r="B418">
-        <v>41100115</v>
+        <v>411001120</v>
       </c>
       <c r="C418" t="s">
-        <v>188</v>
+        <v>746</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -11294,10 +11352,10 @@
         <v>411</v>
       </c>
       <c r="B419">
-        <v>41100116</v>
+        <v>41100113</v>
       </c>
       <c r="C419" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -11305,10 +11363,10 @@
         <v>411</v>
       </c>
       <c r="B420">
-        <v>41100117</v>
+        <v>41100114</v>
       </c>
       <c r="C420" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
@@ -11316,10 +11374,10 @@
         <v>411</v>
       </c>
       <c r="B421">
-        <v>41100118</v>
+        <v>41100115</v>
       </c>
       <c r="C421" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -11327,10 +11385,10 @@
         <v>411</v>
       </c>
       <c r="B422">
-        <v>41100119</v>
+        <v>41100116</v>
       </c>
       <c r="C422" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -11338,10 +11396,10 @@
         <v>411</v>
       </c>
       <c r="B423">
-        <v>41100120</v>
+        <v>41100117</v>
       </c>
       <c r="C423" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
@@ -11349,10 +11407,10 @@
         <v>411</v>
       </c>
       <c r="B424">
-        <v>41100121</v>
+        <v>41100118</v>
       </c>
       <c r="C424" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
@@ -11360,10 +11418,10 @@
         <v>411</v>
       </c>
       <c r="B425">
-        <v>41100122</v>
+        <v>41100119</v>
       </c>
       <c r="C425" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -11371,10 +11429,10 @@
         <v>411</v>
       </c>
       <c r="B426">
-        <v>41100123</v>
+        <v>41100120</v>
       </c>
       <c r="C426" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
@@ -11382,10 +11440,10 @@
         <v>411</v>
       </c>
       <c r="B427">
-        <v>41100124</v>
+        <v>41100121</v>
       </c>
       <c r="C427" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
@@ -11393,10 +11451,10 @@
         <v>411</v>
       </c>
       <c r="B428">
-        <v>41100125</v>
+        <v>41100122</v>
       </c>
       <c r="C428" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
@@ -11404,10 +11462,10 @@
         <v>411</v>
       </c>
       <c r="B429">
-        <v>41100126</v>
+        <v>41100123</v>
       </c>
       <c r="C429" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
@@ -11415,10 +11473,10 @@
         <v>411</v>
       </c>
       <c r="B430">
-        <v>41100127</v>
+        <v>41100124</v>
       </c>
       <c r="C430" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
@@ -11426,10 +11484,10 @@
         <v>411</v>
       </c>
       <c r="B431">
-        <v>41100128</v>
+        <v>41100125</v>
       </c>
       <c r="C431" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
@@ -11437,10 +11495,10 @@
         <v>411</v>
       </c>
       <c r="B432">
-        <v>41100129</v>
+        <v>41100126</v>
       </c>
       <c r="C432" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
@@ -11448,10 +11506,10 @@
         <v>411</v>
       </c>
       <c r="B433">
-        <v>41100131</v>
+        <v>41100127</v>
       </c>
       <c r="C433" t="s">
-        <v>112</v>
+        <v>200</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
@@ -11459,10 +11517,10 @@
         <v>411</v>
       </c>
       <c r="B434">
-        <v>41100132</v>
+        <v>41100128</v>
       </c>
       <c r="C434" t="s">
-        <v>64</v>
+        <v>201</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
@@ -11470,10 +11528,10 @@
         <v>411</v>
       </c>
       <c r="B435">
-        <v>41100133</v>
+        <v>41100129</v>
       </c>
       <c r="C435" t="s">
-        <v>17</v>
+        <v>202</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
@@ -11481,10 +11539,10 @@
         <v>411</v>
       </c>
       <c r="B436">
-        <v>41100134</v>
+        <v>41100131</v>
       </c>
       <c r="C436" t="s">
-        <v>203</v>
+        <v>112</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
@@ -11492,10 +11550,10 @@
         <v>411</v>
       </c>
       <c r="B437">
-        <v>41100135</v>
+        <v>41100132</v>
       </c>
       <c r="C437" t="s">
-        <v>204</v>
+        <v>64</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
@@ -11503,10 +11561,10 @@
         <v>411</v>
       </c>
       <c r="B438">
-        <v>41100136</v>
+        <v>41100133</v>
       </c>
       <c r="C438" t="s">
-        <v>205</v>
+        <v>17</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
@@ -11514,10 +11572,10 @@
         <v>411</v>
       </c>
       <c r="B439">
-        <v>41100137</v>
+        <v>41100134</v>
       </c>
       <c r="C439" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
@@ -11525,10 +11583,10 @@
         <v>411</v>
       </c>
       <c r="B440">
-        <v>41100138</v>
+        <v>41100135</v>
       </c>
       <c r="C440" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
@@ -11536,10 +11594,10 @@
         <v>411</v>
       </c>
       <c r="B441">
-        <v>41100139</v>
+        <v>41100136</v>
       </c>
       <c r="C441" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
@@ -11547,10 +11605,10 @@
         <v>411</v>
       </c>
       <c r="B442">
-        <v>41100140</v>
+        <v>41100137</v>
       </c>
       <c r="C442" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
@@ -11558,10 +11616,10 @@
         <v>411</v>
       </c>
       <c r="B443">
-        <v>41100141</v>
+        <v>41100138</v>
       </c>
       <c r="C443" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
@@ -11569,10 +11627,10 @@
         <v>411</v>
       </c>
       <c r="B444">
-        <v>41100142</v>
+        <v>41100139</v>
       </c>
       <c r="C444" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
@@ -11580,10 +11638,10 @@
         <v>411</v>
       </c>
       <c r="B445">
-        <v>41100143</v>
+        <v>41100140</v>
       </c>
       <c r="C445" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
@@ -11591,10 +11649,10 @@
         <v>411</v>
       </c>
       <c r="B446">
-        <v>41100144</v>
+        <v>41100141</v>
       </c>
       <c r="C446" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
@@ -11602,10 +11660,10 @@
         <v>411</v>
       </c>
       <c r="B447">
-        <v>41100145</v>
+        <v>41100142</v>
       </c>
       <c r="C447" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
@@ -11613,10 +11671,10 @@
         <v>411</v>
       </c>
       <c r="B448">
-        <v>41100146</v>
+        <v>41100143</v>
       </c>
       <c r="C448" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
@@ -11624,10 +11682,10 @@
         <v>411</v>
       </c>
       <c r="B449">
-        <v>41100147</v>
+        <v>41100144</v>
       </c>
       <c r="C449" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -11635,10 +11693,10 @@
         <v>411</v>
       </c>
       <c r="B450">
-        <v>41100148</v>
+        <v>41100145</v>
       </c>
       <c r="C450" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
@@ -11646,10 +11704,10 @@
         <v>411</v>
       </c>
       <c r="B451">
-        <v>41100149</v>
+        <v>41100146</v>
       </c>
       <c r="C451" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
@@ -11657,10 +11715,10 @@
         <v>411</v>
       </c>
       <c r="B452">
-        <v>4110015</v>
+        <v>41100147</v>
       </c>
       <c r="C452" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
@@ -11668,10 +11726,10 @@
         <v>411</v>
       </c>
       <c r="B453">
-        <v>41100150</v>
+        <v>41100148</v>
       </c>
       <c r="C453" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
@@ -11679,10 +11737,10 @@
         <v>411</v>
       </c>
       <c r="B454">
-        <v>41100151</v>
+        <v>41100149</v>
       </c>
       <c r="C454" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
@@ -11690,10 +11748,10 @@
         <v>411</v>
       </c>
       <c r="B455">
-        <v>41100152</v>
+        <v>4110015</v>
       </c>
       <c r="C455" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
@@ -11701,10 +11759,10 @@
         <v>411</v>
       </c>
       <c r="B456">
-        <v>41100153</v>
+        <v>41100150</v>
       </c>
       <c r="C456" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
@@ -11712,10 +11770,10 @@
         <v>411</v>
       </c>
       <c r="B457">
-        <v>41100154</v>
+        <v>41100151</v>
       </c>
       <c r="C457" t="s">
-        <v>13</v>
+        <v>221</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
@@ -11723,10 +11781,10 @@
         <v>411</v>
       </c>
       <c r="B458">
-        <v>41100155</v>
+        <v>41100152</v>
       </c>
       <c r="C458" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
@@ -11734,10 +11792,10 @@
         <v>411</v>
       </c>
       <c r="B459">
-        <v>41100156</v>
+        <v>41100153</v>
       </c>
       <c r="C459" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
@@ -11745,10 +11803,10 @@
         <v>411</v>
       </c>
       <c r="B460">
-        <v>41100157</v>
+        <v>41100154</v>
       </c>
       <c r="C460" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
@@ -11756,10 +11814,10 @@
         <v>411</v>
       </c>
       <c r="B461">
-        <v>41100158</v>
+        <v>41100155</v>
       </c>
       <c r="C461" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
@@ -11767,10 +11825,10 @@
         <v>411</v>
       </c>
       <c r="B462">
-        <v>41100159</v>
+        <v>41100156</v>
       </c>
       <c r="C462" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
@@ -11778,10 +11836,10 @@
         <v>411</v>
       </c>
       <c r="B463">
-        <v>4110016</v>
+        <v>41100157</v>
       </c>
       <c r="C463" t="s">
-        <v>228</v>
+        <v>16</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
@@ -11789,10 +11847,10 @@
         <v>411</v>
       </c>
       <c r="B464">
-        <v>41100160</v>
+        <v>41100158</v>
       </c>
       <c r="C464" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -11800,10 +11858,10 @@
         <v>411</v>
       </c>
       <c r="B465">
-        <v>41100161</v>
+        <v>41100159</v>
       </c>
       <c r="C465" t="s">
-        <v>18</v>
+        <v>227</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
@@ -11811,10 +11869,10 @@
         <v>411</v>
       </c>
       <c r="B466">
-        <v>41100162</v>
+        <v>4110016</v>
       </c>
       <c r="C466" t="s">
-        <v>105</v>
+        <v>228</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
@@ -11822,10 +11880,10 @@
         <v>411</v>
       </c>
       <c r="B467">
-        <v>41100163</v>
+        <v>41100160</v>
       </c>
       <c r="C467" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -11833,10 +11891,10 @@
         <v>411</v>
       </c>
       <c r="B468">
-        <v>41100164</v>
+        <v>41100161</v>
       </c>
       <c r="C468" t="s">
-        <v>231</v>
+        <v>18</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -11844,10 +11902,10 @@
         <v>411</v>
       </c>
       <c r="B469">
-        <v>41100165</v>
+        <v>41100162</v>
       </c>
       <c r="C469" t="s">
-        <v>232</v>
+        <v>105</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
@@ -11855,10 +11913,10 @@
         <v>411</v>
       </c>
       <c r="B470">
-        <v>41100166</v>
+        <v>41100163</v>
       </c>
       <c r="C470" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
@@ -11866,10 +11924,10 @@
         <v>411</v>
       </c>
       <c r="B471">
-        <v>41100167</v>
+        <v>41100164</v>
       </c>
       <c r="C471" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
@@ -11877,10 +11935,10 @@
         <v>411</v>
       </c>
       <c r="B472">
-        <v>41100168</v>
+        <v>41100165</v>
       </c>
       <c r="C472" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
@@ -11888,10 +11946,10 @@
         <v>411</v>
       </c>
       <c r="B473">
-        <v>41100169</v>
+        <v>41100166</v>
       </c>
       <c r="C473" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -11899,10 +11957,10 @@
         <v>411</v>
       </c>
       <c r="B474">
-        <v>4110017</v>
+        <v>41100167</v>
       </c>
       <c r="C474" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -11910,10 +11968,10 @@
         <v>411</v>
       </c>
       <c r="B475">
-        <v>41100170</v>
+        <v>41100168</v>
       </c>
       <c r="C475" t="s">
-        <v>22</v>
+        <v>235</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -11921,10 +11979,10 @@
         <v>411</v>
       </c>
       <c r="B476">
-        <v>41100171</v>
+        <v>41100169</v>
       </c>
       <c r="C476" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -11932,10 +11990,10 @@
         <v>411</v>
       </c>
       <c r="B477">
-        <v>41100172</v>
+        <v>4110017</v>
       </c>
       <c r="C477" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -11943,10 +12001,10 @@
         <v>411</v>
       </c>
       <c r="B478">
-        <v>41100173</v>
+        <v>41100170</v>
       </c>
       <c r="C478" t="s">
-        <v>240</v>
+        <v>22</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
@@ -11954,10 +12012,10 @@
         <v>411</v>
       </c>
       <c r="B479">
-        <v>41100174</v>
+        <v>41100171</v>
       </c>
       <c r="C479" t="s">
-        <v>21</v>
+        <v>238</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -11965,10 +12023,10 @@
         <v>411</v>
       </c>
       <c r="B480">
-        <v>41100175</v>
+        <v>41100172</v>
       </c>
       <c r="C480" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -11976,10 +12034,10 @@
         <v>411</v>
       </c>
       <c r="B481">
-        <v>41100176</v>
+        <v>41100173</v>
       </c>
       <c r="C481" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -11987,10 +12045,10 @@
         <v>411</v>
       </c>
       <c r="B482">
-        <v>41100177</v>
+        <v>41100174</v>
       </c>
       <c r="C482" t="s">
-        <v>243</v>
+        <v>21</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
@@ -11998,10 +12056,10 @@
         <v>411</v>
       </c>
       <c r="B483">
-        <v>41100178</v>
+        <v>41100175</v>
       </c>
       <c r="C483" t="s">
-        <v>23</v>
+        <v>241</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
@@ -12009,10 +12067,10 @@
         <v>411</v>
       </c>
       <c r="B484">
-        <v>41100179</v>
+        <v>41100176</v>
       </c>
       <c r="C484" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
@@ -12020,10 +12078,10 @@
         <v>411</v>
       </c>
       <c r="B485">
-        <v>4110018</v>
+        <v>41100177</v>
       </c>
       <c r="C485" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -12031,10 +12089,10 @@
         <v>411</v>
       </c>
       <c r="B486">
-        <v>41100180</v>
+        <v>41100178</v>
       </c>
       <c r="C486" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
@@ -12042,10 +12100,10 @@
         <v>411</v>
       </c>
       <c r="B487">
-        <v>41100181</v>
+        <v>41100179</v>
       </c>
       <c r="C487" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -12053,10 +12111,10 @@
         <v>411</v>
       </c>
       <c r="B488">
-        <v>41100182</v>
+        <v>4110018</v>
       </c>
       <c r="C488" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
@@ -12064,10 +12122,10 @@
         <v>411</v>
       </c>
       <c r="B489">
-        <v>41100183</v>
+        <v>41100180</v>
       </c>
       <c r="C489" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
@@ -12075,10 +12133,10 @@
         <v>411</v>
       </c>
       <c r="B490">
-        <v>41100184</v>
+        <v>41100181</v>
       </c>
       <c r="C490" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
@@ -12086,10 +12144,10 @@
         <v>411</v>
       </c>
       <c r="B491">
-        <v>41100185</v>
+        <v>41100182</v>
       </c>
       <c r="C491" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
@@ -12097,10 +12155,10 @@
         <v>411</v>
       </c>
       <c r="B492">
-        <v>41100186</v>
+        <v>41100183</v>
       </c>
       <c r="C492" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
@@ -12108,10 +12166,10 @@
         <v>411</v>
       </c>
       <c r="B493">
-        <v>41100187</v>
+        <v>41100184</v>
       </c>
       <c r="C493" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
@@ -12119,10 +12177,10 @@
         <v>411</v>
       </c>
       <c r="B494">
-        <v>41100188</v>
+        <v>41100185</v>
       </c>
       <c r="C494" t="s">
-        <v>61</v>
+        <v>249</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
@@ -12130,10 +12188,10 @@
         <v>411</v>
       </c>
       <c r="B495">
-        <v>41100189</v>
+        <v>41100186</v>
       </c>
       <c r="C495" t="s">
-        <v>251</v>
+        <v>39</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
@@ -12141,10 +12199,10 @@
         <v>411</v>
       </c>
       <c r="B496">
-        <v>41100190</v>
+        <v>41100187</v>
       </c>
       <c r="C496" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
@@ -12152,10 +12210,10 @@
         <v>411</v>
       </c>
       <c r="B497">
-        <v>41100191</v>
+        <v>41100188</v>
       </c>
       <c r="C497" t="s">
-        <v>253</v>
+        <v>61</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
@@ -12163,10 +12221,10 @@
         <v>411</v>
       </c>
       <c r="B498">
-        <v>41100192</v>
+        <v>41100189</v>
       </c>
       <c r="C498" t="s">
-        <v>69</v>
+        <v>251</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
@@ -12174,10 +12232,10 @@
         <v>411</v>
       </c>
       <c r="B499">
-        <v>41100193</v>
+        <v>41100190</v>
       </c>
       <c r="C499" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
@@ -12185,10 +12243,10 @@
         <v>411</v>
       </c>
       <c r="B500">
-        <v>41100194</v>
+        <v>41100191</v>
       </c>
       <c r="C500" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
@@ -12196,10 +12254,10 @@
         <v>411</v>
       </c>
       <c r="B501">
-        <v>41100195</v>
+        <v>41100192</v>
       </c>
       <c r="C501" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
@@ -12207,10 +12265,10 @@
         <v>411</v>
       </c>
       <c r="B502">
-        <v>41100196</v>
+        <v>41100193</v>
       </c>
       <c r="C502" t="s">
-        <v>68</v>
+        <v>254</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
@@ -12218,10 +12276,10 @@
         <v>411</v>
       </c>
       <c r="B503">
-        <v>41100197</v>
+        <v>41100194</v>
       </c>
       <c r="C503" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -12229,10 +12287,10 @@
         <v>411</v>
       </c>
       <c r="B504">
-        <v>41100198</v>
+        <v>41100195</v>
       </c>
       <c r="C504" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
@@ -12240,10 +12298,10 @@
         <v>411</v>
       </c>
       <c r="B505">
-        <v>41100199</v>
+        <v>41100196</v>
       </c>
       <c r="C505" t="s">
-        <v>257</v>
+        <v>68</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -12251,10 +12309,10 @@
         <v>411</v>
       </c>
       <c r="B506">
-        <v>411002</v>
+        <v>41100197</v>
       </c>
       <c r="C506" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
@@ -12262,10 +12320,10 @@
         <v>411</v>
       </c>
       <c r="B507">
-        <v>4110020</v>
+        <v>41100198</v>
       </c>
       <c r="C507" t="s">
-        <v>259</v>
+        <v>73</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -12273,10 +12331,10 @@
         <v>411</v>
       </c>
       <c r="B508">
-        <v>41100200</v>
+        <v>41100199</v>
       </c>
       <c r="C508" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
@@ -12284,10 +12342,10 @@
         <v>411</v>
       </c>
       <c r="B509">
-        <v>41100201</v>
+        <v>411002</v>
       </c>
       <c r="C509" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
@@ -12295,10 +12353,10 @@
         <v>411</v>
       </c>
       <c r="B510">
-        <v>41100202</v>
+        <v>4110020</v>
       </c>
       <c r="C510" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -12306,10 +12364,10 @@
         <v>411</v>
       </c>
       <c r="B511">
-        <v>41100203</v>
+        <v>41100200</v>
       </c>
       <c r="C511" t="s">
-        <v>79</v>
+        <v>260</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
@@ -12317,10 +12375,10 @@
         <v>411</v>
       </c>
       <c r="B512">
-        <v>41100204</v>
+        <v>41100201</v>
       </c>
       <c r="C512" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
@@ -12328,10 +12386,10 @@
         <v>411</v>
       </c>
       <c r="B513">
-        <v>41100205</v>
+        <v>41100202</v>
       </c>
       <c r="C513" t="s">
-        <v>75</v>
+        <v>262</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
@@ -12339,10 +12397,10 @@
         <v>411</v>
       </c>
       <c r="B514">
-        <v>41100206</v>
+        <v>41100203</v>
       </c>
       <c r="C514" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -12350,10 +12408,10 @@
         <v>411</v>
       </c>
       <c r="B515">
-        <v>41100207</v>
+        <v>41100204</v>
       </c>
       <c r="C515" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -12361,10 +12419,10 @@
         <v>411</v>
       </c>
       <c r="B516">
-        <v>41100208</v>
+        <v>41100205</v>
       </c>
       <c r="C516" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
@@ -12372,10 +12430,10 @@
         <v>411</v>
       </c>
       <c r="B517">
-        <v>41100209</v>
+        <v>41100206</v>
       </c>
       <c r="C517" t="s">
-        <v>265</v>
+        <v>81</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -12383,10 +12441,10 @@
         <v>411</v>
       </c>
       <c r="B518">
-        <v>41100210</v>
+        <v>41100207</v>
       </c>
       <c r="C518" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -12394,10 +12452,10 @@
         <v>411</v>
       </c>
       <c r="B519">
-        <v>41100211</v>
+        <v>41100208</v>
       </c>
       <c r="C519" t="s">
-        <v>267</v>
+        <v>80</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -12405,10 +12463,10 @@
         <v>411</v>
       </c>
       <c r="B520">
-        <v>41100212</v>
+        <v>41100209</v>
       </c>
       <c r="C520" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -12416,10 +12474,10 @@
         <v>411</v>
       </c>
       <c r="B521">
-        <v>41100213</v>
+        <v>41100210</v>
       </c>
       <c r="C521" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -12427,10 +12485,10 @@
         <v>411</v>
       </c>
       <c r="B522">
-        <v>41100214</v>
+        <v>41100211</v>
       </c>
       <c r="C522" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -12438,10 +12496,10 @@
         <v>411</v>
       </c>
       <c r="B523">
-        <v>41100215</v>
+        <v>41100212</v>
       </c>
       <c r="C523" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -12449,10 +12507,10 @@
         <v>411</v>
       </c>
       <c r="B524">
-        <v>41100216</v>
+        <v>41100213</v>
       </c>
       <c r="C524" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -12460,10 +12518,10 @@
         <v>411</v>
       </c>
       <c r="B525">
-        <v>41100217</v>
+        <v>41100214</v>
       </c>
       <c r="C525" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -12471,10 +12529,10 @@
         <v>411</v>
       </c>
       <c r="B526">
-        <v>41100218</v>
+        <v>41100215</v>
       </c>
       <c r="C526" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
@@ -12482,10 +12540,10 @@
         <v>411</v>
       </c>
       <c r="B527">
-        <v>41100219</v>
+        <v>41100216</v>
       </c>
       <c r="C527" t="s">
-        <v>82</v>
+        <v>272</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
@@ -12493,10 +12551,10 @@
         <v>411</v>
       </c>
       <c r="B528">
-        <v>41100220</v>
+        <v>41100217</v>
       </c>
       <c r="C528" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -12504,10 +12562,10 @@
         <v>411</v>
       </c>
       <c r="B529">
-        <v>41100221</v>
+        <v>41100218</v>
       </c>
       <c r="C529" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -12515,10 +12573,10 @@
         <v>411</v>
       </c>
       <c r="B530">
-        <v>41100222</v>
+        <v>41100219</v>
       </c>
       <c r="C530" t="s">
-        <v>277</v>
+        <v>82</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -12526,10 +12584,10 @@
         <v>411</v>
       </c>
       <c r="B531">
-        <v>41100223</v>
+        <v>41100220</v>
       </c>
       <c r="C531" t="s">
-        <v>86</v>
+        <v>275</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -12537,10 +12595,10 @@
         <v>411</v>
       </c>
       <c r="B532">
-        <v>41100224</v>
+        <v>41100221</v>
       </c>
       <c r="C532" t="s">
-        <v>83</v>
+        <v>276</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
@@ -12548,10 +12606,10 @@
         <v>411</v>
       </c>
       <c r="B533">
-        <v>41100225</v>
+        <v>41100222</v>
       </c>
       <c r="C533" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -12559,10 +12617,10 @@
         <v>411</v>
       </c>
       <c r="B534">
-        <v>41100226</v>
+        <v>41100223</v>
       </c>
       <c r="C534" t="s">
-        <v>279</v>
+        <v>86</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
@@ -12570,10 +12628,10 @@
         <v>411</v>
       </c>
       <c r="B535">
-        <v>41100227</v>
+        <v>41100224</v>
       </c>
       <c r="C535" t="s">
-        <v>280</v>
+        <v>83</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -12581,10 +12639,10 @@
         <v>411</v>
       </c>
       <c r="B536">
-        <v>41100228</v>
+        <v>41100225</v>
       </c>
       <c r="C536" t="s">
-        <v>85</v>
+        <v>278</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -12592,10 +12650,10 @@
         <v>411</v>
       </c>
       <c r="B537">
-        <v>41100229</v>
+        <v>41100226</v>
       </c>
       <c r="C537" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -12603,10 +12661,10 @@
         <v>411</v>
       </c>
       <c r="B538">
-        <v>4110023</v>
+        <v>41100227</v>
       </c>
       <c r="C538" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -12614,10 +12672,10 @@
         <v>411</v>
       </c>
       <c r="B539">
-        <v>41100230</v>
+        <v>41100228</v>
       </c>
       <c r="C539" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -12625,10 +12683,10 @@
         <v>411</v>
       </c>
       <c r="B540">
-        <v>41100231</v>
+        <v>41100229</v>
       </c>
       <c r="C540" t="s">
-        <v>87</v>
+        <v>281</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -12636,10 +12694,10 @@
         <v>411</v>
       </c>
       <c r="B541">
-        <v>41100232</v>
+        <v>4110023</v>
       </c>
       <c r="C541" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -12647,10 +12705,10 @@
         <v>411</v>
       </c>
       <c r="B542">
-        <v>41100233</v>
+        <v>41100230</v>
       </c>
       <c r="C542" t="s">
-        <v>78</v>
+        <v>11</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
@@ -12658,10 +12716,10 @@
         <v>411</v>
       </c>
       <c r="B543">
-        <v>41100234</v>
+        <v>41100231</v>
       </c>
       <c r="C543" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -12669,10 +12727,10 @@
         <v>411</v>
       </c>
       <c r="B544">
-        <v>41100235</v>
+        <v>41100232</v>
       </c>
       <c r="C544" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -12680,10 +12738,10 @@
         <v>411</v>
       </c>
       <c r="B545">
-        <v>41100236</v>
+        <v>41100233</v>
       </c>
       <c r="C545" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -12691,10 +12749,10 @@
         <v>411</v>
       </c>
       <c r="B546">
-        <v>41100237</v>
+        <v>41100234</v>
       </c>
       <c r="C546" t="s">
-        <v>285</v>
+        <v>88</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -12702,10 +12760,10 @@
         <v>411</v>
       </c>
       <c r="B547">
-        <v>41100238</v>
+        <v>41100235</v>
       </c>
       <c r="C547" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -12713,10 +12771,10 @@
         <v>411</v>
       </c>
       <c r="B548">
-        <v>41100239</v>
+        <v>41100236</v>
       </c>
       <c r="C548" t="s">
-        <v>287</v>
+        <v>89</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -12724,10 +12782,10 @@
         <v>411</v>
       </c>
       <c r="B549">
-        <v>41100240</v>
+        <v>41100237</v>
       </c>
       <c r="C549" t="s">
-        <v>90</v>
+        <v>285</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -12735,10 +12793,10 @@
         <v>411</v>
       </c>
       <c r="B550">
-        <v>41100241</v>
+        <v>41100238</v>
       </c>
       <c r="C550" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -12746,10 +12804,10 @@
         <v>411</v>
       </c>
       <c r="B551">
-        <v>41100242</v>
+        <v>41100239</v>
       </c>
       <c r="C551" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -12757,10 +12815,10 @@
         <v>411</v>
       </c>
       <c r="B552">
-        <v>41100243</v>
+        <v>41100240</v>
       </c>
       <c r="C552" t="s">
-        <v>290</v>
+        <v>90</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -12768,10 +12826,10 @@
         <v>411</v>
       </c>
       <c r="B553">
-        <v>41100244</v>
+        <v>41100241</v>
       </c>
       <c r="C553" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -12779,10 +12837,10 @@
         <v>411</v>
       </c>
       <c r="B554">
-        <v>41100245</v>
+        <v>41100242</v>
       </c>
       <c r="C554" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -12790,10 +12848,10 @@
         <v>411</v>
       </c>
       <c r="B555">
-        <v>41100246</v>
+        <v>41100243</v>
       </c>
       <c r="C555" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -12801,10 +12859,10 @@
         <v>411</v>
       </c>
       <c r="B556">
-        <v>41100247</v>
+        <v>41100244</v>
       </c>
       <c r="C556" t="s">
-        <v>95</v>
+        <v>291</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -12812,10 +12870,10 @@
         <v>411</v>
       </c>
       <c r="B557">
-        <v>41100249</v>
+        <v>41100245</v>
       </c>
       <c r="C557" t="s">
-        <v>36</v>
+        <v>292</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -12823,10 +12881,10 @@
         <v>411</v>
       </c>
       <c r="B558">
-        <v>4110025</v>
+        <v>41100246</v>
       </c>
       <c r="C558" t="s">
-        <v>749</v>
+        <v>293</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -12834,10 +12892,10 @@
         <v>411</v>
       </c>
       <c r="B559">
-        <v>41100250</v>
+        <v>41100247</v>
       </c>
       <c r="C559" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -12845,10 +12903,10 @@
         <v>411</v>
       </c>
       <c r="B560">
-        <v>41100251</v>
+        <v>41100249</v>
       </c>
       <c r="C560" t="s">
-        <v>295</v>
+        <v>36</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -12856,10 +12914,10 @@
         <v>411</v>
       </c>
       <c r="B561">
-        <v>41100252</v>
+        <v>4110025</v>
       </c>
       <c r="C561" t="s">
-        <v>296</v>
+        <v>749</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
@@ -12867,10 +12925,10 @@
         <v>411</v>
       </c>
       <c r="B562">
-        <v>41100253</v>
+        <v>41100250</v>
       </c>
       <c r="C562" t="s">
-        <v>297</v>
+        <v>92</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
@@ -12878,10 +12936,10 @@
         <v>411</v>
       </c>
       <c r="B563">
-        <v>41100254</v>
+        <v>41100251</v>
       </c>
       <c r="C563" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
@@ -12889,10 +12947,10 @@
         <v>411</v>
       </c>
       <c r="B564">
-        <v>41100255</v>
+        <v>41100252</v>
       </c>
       <c r="C564" t="s">
-        <v>96</v>
+        <v>296</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -12900,10 +12958,10 @@
         <v>411</v>
       </c>
       <c r="B565">
-        <v>41100256</v>
+        <v>41100253</v>
       </c>
       <c r="C565" t="s">
-        <v>93</v>
+        <v>297</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -12911,10 +12969,10 @@
         <v>411</v>
       </c>
       <c r="B566">
-        <v>41100257</v>
+        <v>41100254</v>
       </c>
       <c r="C566" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -12922,10 +12980,10 @@
         <v>411</v>
       </c>
       <c r="B567">
-        <v>41100258</v>
+        <v>41100255</v>
       </c>
       <c r="C567" t="s">
-        <v>300</v>
+        <v>96</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
@@ -12933,10 +12991,10 @@
         <v>411</v>
       </c>
       <c r="B568">
-        <v>41100259</v>
+        <v>41100256</v>
       </c>
       <c r="C568" t="s">
-        <v>301</v>
+        <v>93</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -12944,10 +13002,10 @@
         <v>411</v>
       </c>
       <c r="B569">
-        <v>4110026</v>
+        <v>41100257</v>
       </c>
       <c r="C569" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -12955,10 +13013,10 @@
         <v>411</v>
       </c>
       <c r="B570">
-        <v>41100260</v>
+        <v>41100258</v>
       </c>
       <c r="C570" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -12966,10 +13024,10 @@
         <v>411</v>
       </c>
       <c r="B571">
-        <v>41100261</v>
+        <v>41100259</v>
       </c>
       <c r="C571" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -12977,10 +13035,10 @@
         <v>411</v>
       </c>
       <c r="B572">
-        <v>41100262</v>
+        <v>4110026</v>
       </c>
       <c r="C572" t="s">
-        <v>97</v>
+        <v>302</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -12988,10 +13046,10 @@
         <v>411</v>
       </c>
       <c r="B573">
-        <v>41100263</v>
+        <v>41100260</v>
       </c>
       <c r="C573" t="s">
-        <v>98</v>
+        <v>303</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -12999,10 +13057,10 @@
         <v>411</v>
       </c>
       <c r="B574">
-        <v>41100264</v>
+        <v>41100261</v>
       </c>
       <c r="C574" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
@@ -13010,10 +13068,10 @@
         <v>411</v>
       </c>
       <c r="B575">
-        <v>41100265</v>
+        <v>41100262</v>
       </c>
       <c r="C575" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -13021,10 +13079,10 @@
         <v>411</v>
       </c>
       <c r="B576">
-        <v>41100266</v>
+        <v>41100263</v>
       </c>
       <c r="C576" t="s">
-        <v>306</v>
+        <v>98</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -13032,10 +13090,10 @@
         <v>411</v>
       </c>
       <c r="B577">
-        <v>41100267</v>
+        <v>41100264</v>
       </c>
       <c r="C577" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -13043,10 +13101,10 @@
         <v>411</v>
       </c>
       <c r="B578">
-        <v>41100268</v>
+        <v>41100265</v>
       </c>
       <c r="C578" t="s">
-        <v>308</v>
+        <v>99</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -13054,10 +13112,10 @@
         <v>411</v>
       </c>
       <c r="B579">
-        <v>41100269</v>
+        <v>41100266</v>
       </c>
       <c r="C579" t="s">
-        <v>34</v>
+        <v>306</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -13065,10 +13123,10 @@
         <v>411</v>
       </c>
       <c r="B580">
-        <v>41100270</v>
+        <v>41100267</v>
       </c>
       <c r="C580" t="s">
-        <v>747</v>
+        <v>307</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -13076,10 +13134,10 @@
         <v>411</v>
       </c>
       <c r="B581">
-        <v>411002700</v>
+        <v>41100268</v>
       </c>
       <c r="C581" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -13087,10 +13145,10 @@
         <v>411</v>
       </c>
       <c r="B582">
-        <v>41100271</v>
+        <v>41100269</v>
       </c>
       <c r="C582" t="s">
-        <v>310</v>
+        <v>34</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -13098,10 +13156,10 @@
         <v>411</v>
       </c>
       <c r="B583">
-        <v>41100272</v>
+        <v>41100270</v>
       </c>
       <c r="C583" t="s">
-        <v>311</v>
+        <v>747</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -13109,10 +13167,10 @@
         <v>411</v>
       </c>
       <c r="B584">
-        <v>41100273</v>
+        <v>411002700</v>
       </c>
       <c r="C584" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -13120,10 +13178,10 @@
         <v>411</v>
       </c>
       <c r="B585">
-        <v>41100274</v>
+        <v>41100271</v>
       </c>
       <c r="C585" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -13131,10 +13189,10 @@
         <v>411</v>
       </c>
       <c r="B586">
-        <v>41100275</v>
+        <v>41100272</v>
       </c>
       <c r="C586" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -13142,10 +13200,10 @@
         <v>411</v>
       </c>
       <c r="B587">
-        <v>41100276</v>
+        <v>41100273</v>
       </c>
       <c r="C587" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -13153,10 +13211,10 @@
         <v>411</v>
       </c>
       <c r="B588">
-        <v>41100277</v>
+        <v>41100274</v>
       </c>
       <c r="C588" t="s">
-        <v>103</v>
+        <v>313</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -13164,10 +13222,10 @@
         <v>411</v>
       </c>
       <c r="B589">
-        <v>41100278</v>
+        <v>41100275</v>
       </c>
       <c r="C589" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -13175,10 +13233,10 @@
         <v>411</v>
       </c>
       <c r="B590">
-        <v>41100279</v>
+        <v>41100276</v>
       </c>
       <c r="C590" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -13186,10 +13244,10 @@
         <v>411</v>
       </c>
       <c r="B591">
-        <v>41100280</v>
+        <v>41100277</v>
       </c>
       <c r="C591" t="s">
-        <v>317</v>
+        <v>103</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -13197,10 +13255,10 @@
         <v>411</v>
       </c>
       <c r="B592">
-        <v>41100281</v>
+        <v>41100278</v>
       </c>
       <c r="C592" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -13208,10 +13266,10 @@
         <v>411</v>
       </c>
       <c r="B593">
-        <v>41100282</v>
+        <v>41100279</v>
       </c>
       <c r="C593" t="s">
-        <v>104</v>
+        <v>294</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -13219,10 +13277,10 @@
         <v>411</v>
       </c>
       <c r="B594">
-        <v>41100283</v>
+        <v>41100280</v>
       </c>
       <c r="C594" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -13230,10 +13288,10 @@
         <v>411</v>
       </c>
       <c r="B595">
-        <v>41100284</v>
+        <v>41100281</v>
       </c>
       <c r="C595" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -13241,10 +13299,10 @@
         <v>411</v>
       </c>
       <c r="B596">
-        <v>41100285</v>
+        <v>41100282</v>
       </c>
       <c r="C596" t="s">
-        <v>321</v>
+        <v>104</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -13252,10 +13310,10 @@
         <v>411</v>
       </c>
       <c r="B597">
-        <v>41100286</v>
+        <v>41100283</v>
       </c>
       <c r="C597" t="s">
-        <v>102</v>
+        <v>319</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -13263,10 +13321,10 @@
         <v>411</v>
       </c>
       <c r="B598">
-        <v>41100287</v>
+        <v>41100284</v>
       </c>
       <c r="C598" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -13274,10 +13332,10 @@
         <v>411</v>
       </c>
       <c r="B599">
-        <v>41100288</v>
+        <v>41100285</v>
       </c>
       <c r="C599" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -13285,10 +13343,10 @@
         <v>411</v>
       </c>
       <c r="B600">
-        <v>41100289</v>
+        <v>41100286</v>
       </c>
       <c r="C600" t="s">
-        <v>324</v>
+        <v>102</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -13296,10 +13354,10 @@
         <v>411</v>
       </c>
       <c r="B601">
-        <v>4110029</v>
+        <v>41100287</v>
       </c>
       <c r="C601" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -13307,10 +13365,10 @@
         <v>411</v>
       </c>
       <c r="B602">
-        <v>41100290</v>
+        <v>41100288</v>
       </c>
       <c r="C602" t="s">
-        <v>100</v>
+        <v>323</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -13318,10 +13376,10 @@
         <v>411</v>
       </c>
       <c r="B603">
-        <v>41100291</v>
+        <v>41100289</v>
       </c>
       <c r="C603" t="s">
-        <v>101</v>
+        <v>324</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -13329,10 +13387,10 @@
         <v>411</v>
       </c>
       <c r="B604">
-        <v>41100292</v>
+        <v>4110029</v>
       </c>
       <c r="C604" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -13340,10 +13398,10 @@
         <v>411</v>
       </c>
       <c r="B605">
-        <v>41100293</v>
+        <v>41100290</v>
       </c>
       <c r="C605" t="s">
-        <v>327</v>
+        <v>100</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -13351,10 +13409,10 @@
         <v>411</v>
       </c>
       <c r="B606">
-        <v>41100294</v>
+        <v>41100291</v>
       </c>
       <c r="C606" t="s">
-        <v>328</v>
+        <v>101</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -13362,10 +13420,10 @@
         <v>411</v>
       </c>
       <c r="B607">
-        <v>41100295</v>
+        <v>41100292</v>
       </c>
       <c r="C607" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -13373,10 +13431,10 @@
         <v>411</v>
       </c>
       <c r="B608">
-        <v>41100296</v>
+        <v>41100293</v>
       </c>
       <c r="C608" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -13384,10 +13442,10 @@
         <v>411</v>
       </c>
       <c r="B609">
-        <v>41100297</v>
+        <v>41100294</v>
       </c>
       <c r="C609" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -13395,10 +13453,10 @@
         <v>411</v>
       </c>
       <c r="B610">
-        <v>41100298</v>
+        <v>41100295</v>
       </c>
       <c r="C610" t="s">
-        <v>106</v>
+        <v>329</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -13406,10 +13464,10 @@
         <v>411</v>
       </c>
       <c r="B611">
-        <v>41100299</v>
+        <v>41100296</v>
       </c>
       <c r="C611" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -13417,10 +13475,10 @@
         <v>411</v>
       </c>
       <c r="B612">
-        <v>411003</v>
+        <v>41100297</v>
       </c>
       <c r="C612" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -13428,10 +13486,10 @@
         <v>411</v>
       </c>
       <c r="B613">
-        <v>41100300</v>
+        <v>41100298</v>
       </c>
       <c r="C613" t="s">
-        <v>334</v>
+        <v>106</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -13439,10 +13497,10 @@
         <v>411</v>
       </c>
       <c r="B614">
-        <v>41100301</v>
+        <v>41100299</v>
       </c>
       <c r="C614" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -13450,10 +13508,10 @@
         <v>411</v>
       </c>
       <c r="B615">
-        <v>41100302</v>
+        <v>411003</v>
       </c>
       <c r="C615" t="s">
-        <v>107</v>
+        <v>333</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -13461,10 +13519,10 @@
         <v>411</v>
       </c>
       <c r="B616">
-        <v>41100303</v>
+        <v>41100300</v>
       </c>
       <c r="C616" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -13472,10 +13530,10 @@
         <v>411</v>
       </c>
       <c r="B617">
-        <v>41100304</v>
+        <v>41100301</v>
       </c>
       <c r="C617" t="s">
-        <v>108</v>
+        <v>335</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -13483,10 +13541,10 @@
         <v>411</v>
       </c>
       <c r="B618">
-        <v>41100305</v>
+        <v>41100302</v>
       </c>
       <c r="C618" t="s">
-        <v>337</v>
+        <v>107</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -13494,10 +13552,10 @@
         <v>411</v>
       </c>
       <c r="B619">
-        <v>41100306</v>
+        <v>41100303</v>
       </c>
       <c r="C619" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -13505,10 +13563,10 @@
         <v>411</v>
       </c>
       <c r="B620">
-        <v>41100307</v>
+        <v>41100304</v>
       </c>
       <c r="C620" t="s">
-        <v>339</v>
+        <v>108</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -13516,10 +13574,10 @@
         <v>411</v>
       </c>
       <c r="B621">
-        <v>41100308</v>
+        <v>41100305</v>
       </c>
       <c r="C621" t="s">
-        <v>111</v>
+        <v>337</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -13527,10 +13585,10 @@
         <v>411</v>
       </c>
       <c r="B622">
-        <v>41100309</v>
+        <v>41100306</v>
       </c>
       <c r="C622" t="s">
-        <v>110</v>
+        <v>338</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -13538,10 +13596,10 @@
         <v>411</v>
       </c>
       <c r="B623">
-        <v>41100310</v>
+        <v>41100307</v>
       </c>
       <c r="C623" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -13549,10 +13607,10 @@
         <v>411</v>
       </c>
       <c r="B624">
-        <v>41100311</v>
+        <v>41100308</v>
       </c>
       <c r="C624" t="s">
-        <v>341</v>
+        <v>111</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -13560,10 +13618,10 @@
         <v>411</v>
       </c>
       <c r="B625">
-        <v>41100312</v>
+        <v>41100309</v>
       </c>
       <c r="C625" t="s">
-        <v>342</v>
+        <v>110</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -13571,10 +13629,10 @@
         <v>411</v>
       </c>
       <c r="B626">
-        <v>41100313</v>
+        <v>41100310</v>
       </c>
       <c r="C626" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -13582,10 +13640,10 @@
         <v>411</v>
       </c>
       <c r="B627">
-        <v>41100314</v>
+        <v>41100311</v>
       </c>
       <c r="C627" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -13593,10 +13651,10 @@
         <v>411</v>
       </c>
       <c r="B628">
-        <v>41100315</v>
+        <v>41100312</v>
       </c>
       <c r="C628" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -13604,10 +13662,10 @@
         <v>411</v>
       </c>
       <c r="B629">
-        <v>41100316</v>
+        <v>41100313</v>
       </c>
       <c r="C629" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -13615,10 +13673,10 @@
         <v>411</v>
       </c>
       <c r="B630">
-        <v>41100317</v>
+        <v>41100314</v>
       </c>
       <c r="C630" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -13626,10 +13684,10 @@
         <v>411</v>
       </c>
       <c r="B631">
-        <v>41100318</v>
+        <v>41100315</v>
       </c>
       <c r="C631" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -13637,10 +13695,10 @@
         <v>411</v>
       </c>
       <c r="B632">
-        <v>41100319</v>
+        <v>41100316</v>
       </c>
       <c r="C632" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -13648,10 +13706,10 @@
         <v>411</v>
       </c>
       <c r="B633">
-        <v>41100320</v>
+        <v>41100317</v>
       </c>
       <c r="C633" t="s">
-        <v>113</v>
+        <v>347</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -13659,10 +13717,10 @@
         <v>411</v>
       </c>
       <c r="B634">
-        <v>41100321</v>
+        <v>41100318</v>
       </c>
       <c r="C634" t="s">
-        <v>114</v>
+        <v>348</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
@@ -13670,10 +13728,10 @@
         <v>411</v>
       </c>
       <c r="B635">
-        <v>41100322</v>
+        <v>41100319</v>
       </c>
       <c r="C635" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
@@ -13681,10 +13739,10 @@
         <v>411</v>
       </c>
       <c r="B636">
-        <v>41100323</v>
+        <v>41100320</v>
       </c>
       <c r="C636" t="s">
-        <v>352</v>
+        <v>113</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
@@ -13692,10 +13750,10 @@
         <v>411</v>
       </c>
       <c r="B637">
-        <v>41100324</v>
+        <v>41100321</v>
       </c>
       <c r="C637" t="s">
-        <v>353</v>
+        <v>114</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
@@ -13703,10 +13761,10 @@
         <v>411</v>
       </c>
       <c r="B638">
-        <v>41100325</v>
+        <v>41100322</v>
       </c>
       <c r="C638" t="s">
-        <v>115</v>
+        <v>351</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -13714,10 +13772,10 @@
         <v>411</v>
       </c>
       <c r="B639">
-        <v>41100326</v>
+        <v>41100323</v>
       </c>
       <c r="C639" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -13725,10 +13783,10 @@
         <v>411</v>
       </c>
       <c r="B640">
-        <v>41100327</v>
+        <v>41100324</v>
       </c>
       <c r="C640" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
@@ -13736,10 +13794,10 @@
         <v>411</v>
       </c>
       <c r="B641">
-        <v>41100328</v>
+        <v>41100325</v>
       </c>
       <c r="C641" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
@@ -13747,10 +13805,10 @@
         <v>411</v>
       </c>
       <c r="B642">
-        <v>41100329</v>
+        <v>41100326</v>
       </c>
       <c r="C642" t="s">
-        <v>123</v>
+        <v>354</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
@@ -13758,10 +13816,10 @@
         <v>411</v>
       </c>
       <c r="B643">
-        <v>4110033</v>
+        <v>41100327</v>
       </c>
       <c r="C643" t="s">
-        <v>749</v>
+        <v>355</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
@@ -13769,10 +13827,10 @@
         <v>411</v>
       </c>
       <c r="B644">
-        <v>41100330</v>
+        <v>41100328</v>
       </c>
       <c r="C644" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -13780,10 +13838,10 @@
         <v>411</v>
       </c>
       <c r="B645">
-        <v>41100331</v>
+        <v>41100329</v>
       </c>
       <c r="C645" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -13791,10 +13849,10 @@
         <v>411</v>
       </c>
       <c r="B646">
-        <v>41100332</v>
+        <v>4110033</v>
       </c>
       <c r="C646" t="s">
-        <v>357</v>
+        <v>749</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -13802,10 +13860,10 @@
         <v>411</v>
       </c>
       <c r="B647">
-        <v>41100333</v>
+        <v>41100330</v>
       </c>
       <c r="C647" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -13813,10 +13871,10 @@
         <v>411</v>
       </c>
       <c r="B648">
-        <v>41100334</v>
+        <v>41100331</v>
       </c>
       <c r="C648" t="s">
-        <v>358</v>
+        <v>121</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -13824,10 +13882,10 @@
         <v>411</v>
       </c>
       <c r="B649">
-        <v>41100335</v>
+        <v>41100332</v>
       </c>
       <c r="C649" t="s">
-        <v>124</v>
+        <v>357</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -13835,10 +13893,10 @@
         <v>411</v>
       </c>
       <c r="B650">
-        <v>41100336</v>
+        <v>41100333</v>
       </c>
       <c r="C650" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -13846,10 +13904,10 @@
         <v>411</v>
       </c>
       <c r="B651">
-        <v>41100337</v>
+        <v>41100334</v>
       </c>
       <c r="C651" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -13857,10 +13915,10 @@
         <v>411</v>
       </c>
       <c r="B652">
-        <v>41100338</v>
+        <v>41100335</v>
       </c>
       <c r="C652" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -13868,10 +13926,10 @@
         <v>411</v>
       </c>
       <c r="B653">
-        <v>41100339</v>
+        <v>41100336</v>
       </c>
       <c r="C653" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -13879,10 +13937,10 @@
         <v>411</v>
       </c>
       <c r="B654">
-        <v>41100340</v>
+        <v>41100337</v>
       </c>
       <c r="C654" t="s">
-        <v>117</v>
+        <v>359</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -13890,10 +13948,10 @@
         <v>411</v>
       </c>
       <c r="B655">
-        <v>41100341</v>
+        <v>41100338</v>
       </c>
       <c r="C655" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
@@ -13901,10 +13959,10 @@
         <v>411</v>
       </c>
       <c r="B656">
-        <v>41100342</v>
+        <v>41100339</v>
       </c>
       <c r="C656" t="s">
-        <v>360</v>
+        <v>119</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -13912,10 +13970,10 @@
         <v>411</v>
       </c>
       <c r="B657">
-        <v>41100343</v>
+        <v>41100340</v>
       </c>
       <c r="C657" t="s">
-        <v>361</v>
+        <v>117</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -13923,10 +13981,10 @@
         <v>411</v>
       </c>
       <c r="B658">
-        <v>41100344</v>
+        <v>41100341</v>
       </c>
       <c r="C658" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -13934,10 +13992,10 @@
         <v>411</v>
       </c>
       <c r="B659">
-        <v>41100345</v>
+        <v>41100342</v>
       </c>
       <c r="C659" t="s">
-        <v>128</v>
+        <v>360</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
@@ -13945,10 +14003,10 @@
         <v>411</v>
       </c>
       <c r="B660">
-        <v>41100346</v>
+        <v>41100343</v>
       </c>
       <c r="C660" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
@@ -13956,10 +14014,10 @@
         <v>411</v>
       </c>
       <c r="B661">
-        <v>41100347</v>
+        <v>41100344</v>
       </c>
       <c r="C661" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
@@ -13967,10 +14025,10 @@
         <v>411</v>
       </c>
       <c r="B662">
-        <v>41100348</v>
+        <v>41100345</v>
       </c>
       <c r="C662" t="s">
-        <v>363</v>
+        <v>128</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -13978,10 +14036,10 @@
         <v>411</v>
       </c>
       <c r="B663">
-        <v>41100349</v>
+        <v>41100346</v>
       </c>
       <c r="C663" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -13989,10 +14047,10 @@
         <v>411</v>
       </c>
       <c r="B664">
-        <v>41100350</v>
+        <v>41100347</v>
       </c>
       <c r="C664" t="s">
-        <v>365</v>
+        <v>14</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -14000,10 +14058,10 @@
         <v>411</v>
       </c>
       <c r="B665">
-        <v>41100351</v>
+        <v>41100348</v>
       </c>
       <c r="C665" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -14011,10 +14069,10 @@
         <v>411</v>
       </c>
       <c r="B666">
-        <v>41100352</v>
+        <v>41100349</v>
       </c>
       <c r="C666" t="s">
-        <v>130</v>
+        <v>364</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -14022,10 +14080,10 @@
         <v>411</v>
       </c>
       <c r="B667">
-        <v>41100353</v>
+        <v>41100350</v>
       </c>
       <c r="C667" t="s">
-        <v>15</v>
+        <v>365</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
@@ -14033,10 +14091,10 @@
         <v>411</v>
       </c>
       <c r="B668">
-        <v>41100354</v>
+        <v>41100351</v>
       </c>
       <c r="C668" t="s">
-        <v>131</v>
+        <v>366</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
@@ -14044,10 +14102,10 @@
         <v>411</v>
       </c>
       <c r="B669">
-        <v>41100355</v>
+        <v>41100352</v>
       </c>
       <c r="C669" t="s">
-        <v>367</v>
+        <v>130</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
@@ -14055,10 +14113,10 @@
         <v>411</v>
       </c>
       <c r="B670">
-        <v>41100356</v>
+        <v>41100353</v>
       </c>
       <c r="C670" t="s">
-        <v>132</v>
+        <v>15</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
@@ -14066,10 +14124,10 @@
         <v>411</v>
       </c>
       <c r="B671">
-        <v>41100357</v>
+        <v>41100354</v>
       </c>
       <c r="C671" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
@@ -14077,10 +14135,10 @@
         <v>411</v>
       </c>
       <c r="B672">
-        <v>41100358</v>
+        <v>41100355</v>
       </c>
       <c r="C672" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
@@ -14088,10 +14146,10 @@
         <v>411</v>
       </c>
       <c r="B673">
-        <v>41100359</v>
+        <v>41100356</v>
       </c>
       <c r="C673" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.25">
@@ -14099,10 +14157,10 @@
         <v>411</v>
       </c>
       <c r="B674">
-        <v>41100360</v>
+        <v>41100357</v>
       </c>
       <c r="C674" t="s">
-        <v>369</v>
+        <v>133</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
@@ -14110,10 +14168,10 @@
         <v>411</v>
       </c>
       <c r="B675">
-        <v>41100361</v>
+        <v>41100358</v>
       </c>
       <c r="C675" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
@@ -14121,10 +14179,10 @@
         <v>411</v>
       </c>
       <c r="B676">
-        <v>41100362</v>
+        <v>41100359</v>
       </c>
       <c r="C676" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.25">
@@ -14132,10 +14190,10 @@
         <v>411</v>
       </c>
       <c r="B677">
-        <v>41100363</v>
+        <v>41100360</v>
       </c>
       <c r="C677" t="s">
-        <v>136</v>
+        <v>369</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
@@ -14143,10 +14201,10 @@
         <v>411</v>
       </c>
       <c r="B678">
-        <v>41100364</v>
+        <v>41100361</v>
       </c>
       <c r="C678" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
@@ -14154,10 +14212,10 @@
         <v>411</v>
       </c>
       <c r="B679">
-        <v>41100365</v>
+        <v>41100362</v>
       </c>
       <c r="C679" t="s">
-        <v>372</v>
+        <v>135</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
@@ -14165,10 +14223,10 @@
         <v>411</v>
       </c>
       <c r="B680">
-        <v>41100366</v>
+        <v>41100363</v>
       </c>
       <c r="C680" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
@@ -14176,10 +14234,10 @@
         <v>411</v>
       </c>
       <c r="B681">
-        <v>41100367</v>
+        <v>41100364</v>
       </c>
       <c r="C681" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
@@ -14187,10 +14245,10 @@
         <v>411</v>
       </c>
       <c r="B682">
-        <v>41100368</v>
+        <v>41100365</v>
       </c>
       <c r="C682" t="s">
-        <v>138</v>
+        <v>372</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
@@ -14198,10 +14256,10 @@
         <v>411</v>
       </c>
       <c r="B683">
-        <v>41100369</v>
+        <v>41100366</v>
       </c>
       <c r="C683" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -14209,10 +14267,10 @@
         <v>411</v>
       </c>
       <c r="B684">
-        <v>41100370</v>
+        <v>41100367</v>
       </c>
       <c r="C684" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
@@ -14220,10 +14278,10 @@
         <v>411</v>
       </c>
       <c r="B685">
-        <v>41100371</v>
+        <v>41100368</v>
       </c>
       <c r="C685" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
@@ -14231,10 +14289,10 @@
         <v>411</v>
       </c>
       <c r="B686">
-        <v>41100372</v>
+        <v>41100369</v>
       </c>
       <c r="C686" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
@@ -14242,10 +14300,10 @@
         <v>411</v>
       </c>
       <c r="B687">
-        <v>41100373</v>
+        <v>41100370</v>
       </c>
       <c r="C687" t="s">
-        <v>143</v>
+        <v>374</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.25">
@@ -14253,10 +14311,10 @@
         <v>411</v>
       </c>
       <c r="B688">
-        <v>41100374</v>
+        <v>41100371</v>
       </c>
       <c r="C688" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.25">
@@ -14264,10 +14322,10 @@
         <v>411</v>
       </c>
       <c r="B689">
-        <v>41100375</v>
+        <v>41100372</v>
       </c>
       <c r="C689" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.25">
@@ -14275,10 +14333,10 @@
         <v>411</v>
       </c>
       <c r="B690">
-        <v>41100376</v>
+        <v>41100373</v>
       </c>
       <c r="C690" t="s">
-        <v>375</v>
+        <v>143</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.25">
@@ -14286,10 +14344,10 @@
         <v>411</v>
       </c>
       <c r="B691">
-        <v>41100377</v>
+        <v>41100374</v>
       </c>
       <c r="C691" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.25">
@@ -14297,10 +14355,10 @@
         <v>411</v>
       </c>
       <c r="B692">
-        <v>41100378</v>
+        <v>41100375</v>
       </c>
       <c r="C692" t="s">
-        <v>376</v>
+        <v>146</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.25">
@@ -14308,10 +14366,10 @@
         <v>411</v>
       </c>
       <c r="B693">
-        <v>41100379</v>
+        <v>41100376</v>
       </c>
       <c r="C693" t="s">
-        <v>151</v>
+        <v>375</v>
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.25">
@@ -14319,10 +14377,10 @@
         <v>411</v>
       </c>
       <c r="B694">
-        <v>4110038</v>
+        <v>41100377</v>
       </c>
       <c r="C694" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.25">
@@ -14330,10 +14388,10 @@
         <v>411</v>
       </c>
       <c r="B695">
-        <v>41100380</v>
+        <v>41100378</v>
       </c>
       <c r="C695" t="s">
-        <v>156</v>
+        <v>376</v>
       </c>
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.25">
@@ -14341,10 +14399,10 @@
         <v>411</v>
       </c>
       <c r="B696">
-        <v>41100381</v>
+        <v>41100379</v>
       </c>
       <c r="C696" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.25">
@@ -14352,10 +14410,10 @@
         <v>411</v>
       </c>
       <c r="B697">
-        <v>411004</v>
+        <v>4110038</v>
       </c>
       <c r="C697" t="s">
-        <v>377</v>
+        <v>153</v>
       </c>
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.25">
@@ -14363,10 +14421,10 @@
         <v>411</v>
       </c>
       <c r="B698">
-        <v>41100400</v>
+        <v>41100380</v>
       </c>
       <c r="C698" t="s">
-        <v>49</v>
+        <v>156</v>
       </c>
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.25">
@@ -14374,10 +14432,10 @@
         <v>411</v>
       </c>
       <c r="B699">
-        <v>41100401</v>
+        <v>41100381</v>
       </c>
       <c r="C699" t="s">
-        <v>378</v>
+        <v>154</v>
       </c>
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.25">
@@ -14385,10 +14443,10 @@
         <v>411</v>
       </c>
       <c r="B700">
-        <v>41100402</v>
+        <v>411004</v>
       </c>
       <c r="C700" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.25">
@@ -14396,10 +14454,10 @@
         <v>411</v>
       </c>
       <c r="B701">
-        <v>41100403</v>
+        <v>41100400</v>
       </c>
       <c r="C701" t="s">
-        <v>380</v>
+        <v>49</v>
       </c>
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.25">
@@ -14407,10 +14465,10 @@
         <v>411</v>
       </c>
       <c r="B702">
-        <v>41100404</v>
+        <v>41100401</v>
       </c>
       <c r="C702" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.25">
@@ -14418,10 +14476,10 @@
         <v>411</v>
       </c>
       <c r="B703">
-        <v>41100405</v>
+        <v>41100402</v>
       </c>
       <c r="C703" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.25">
@@ -14429,10 +14487,10 @@
         <v>411</v>
       </c>
       <c r="B704">
-        <v>41100406</v>
+        <v>41100403</v>
       </c>
       <c r="C704" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.25">
@@ -14440,10 +14498,10 @@
         <v>411</v>
       </c>
       <c r="B705">
-        <v>41100407</v>
+        <v>41100404</v>
       </c>
       <c r="C705" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.25">
@@ -14451,10 +14509,10 @@
         <v>411</v>
       </c>
       <c r="B706">
-        <v>41100408</v>
+        <v>41100405</v>
       </c>
       <c r="C706" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.25">
@@ -14462,10 +14520,10 @@
         <v>411</v>
       </c>
       <c r="B707">
-        <v>41100409</v>
+        <v>41100406</v>
       </c>
       <c r="C707" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.25">
@@ -14473,10 +14531,10 @@
         <v>411</v>
       </c>
       <c r="B708">
-        <v>41100410</v>
+        <v>41100407</v>
       </c>
       <c r="C708" t="s">
-        <v>67</v>
+        <v>384</v>
       </c>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.25">
@@ -14484,10 +14542,10 @@
         <v>411</v>
       </c>
       <c r="B709">
-        <v>41100411</v>
+        <v>41100408</v>
       </c>
       <c r="C709" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.25">
@@ -14495,10 +14553,10 @@
         <v>411</v>
       </c>
       <c r="B710">
-        <v>41100415</v>
+        <v>41100409</v>
       </c>
       <c r="C710" t="s">
-        <v>2</v>
+        <v>386</v>
       </c>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.25">
@@ -14506,10 +14564,10 @@
         <v>411</v>
       </c>
       <c r="B711">
-        <v>41100417</v>
+        <v>41100410</v>
       </c>
       <c r="C711" t="s">
-        <v>388</v>
+        <v>67</v>
       </c>
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.25">
@@ -14517,10 +14575,10 @@
         <v>411</v>
       </c>
       <c r="B712">
-        <v>41100418</v>
+        <v>41100411</v>
       </c>
       <c r="C712" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="713" spans="1:3" x14ac:dyDescent="0.25">
@@ -14528,10 +14586,10 @@
         <v>411</v>
       </c>
       <c r="B713">
-        <v>41100420</v>
+        <v>41100415</v>
       </c>
       <c r="C713" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.25">
@@ -14539,10 +14597,10 @@
         <v>411</v>
       </c>
       <c r="B714">
-        <v>41100424</v>
+        <v>41100417</v>
       </c>
       <c r="C714" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.25">
@@ -14550,10 +14608,10 @@
         <v>411</v>
       </c>
       <c r="B715">
-        <v>41100426</v>
+        <v>41100418</v>
       </c>
       <c r="C715" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.25">
@@ -14561,10 +14619,10 @@
         <v>411</v>
       </c>
       <c r="B716">
-        <v>41100427</v>
+        <v>41100420</v>
       </c>
       <c r="C716" t="s">
-        <v>392</v>
+        <v>28</v>
       </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.25">
@@ -14572,10 +14630,10 @@
         <v>411</v>
       </c>
       <c r="B717">
-        <v>41100428</v>
+        <v>41100424</v>
       </c>
       <c r="C717" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.25">
@@ -14583,10 +14641,10 @@
         <v>411</v>
       </c>
       <c r="B718">
-        <v>41100429</v>
+        <v>41100426</v>
       </c>
       <c r="C718" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.25">
@@ -14594,10 +14652,10 @@
         <v>411</v>
       </c>
       <c r="B719">
-        <v>4110043</v>
+        <v>41100427</v>
       </c>
       <c r="C719" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.25">
@@ -14605,10 +14663,10 @@
         <v>411</v>
       </c>
       <c r="B720">
-        <v>41100430</v>
+        <v>41100428</v>
       </c>
       <c r="C720" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.25">
@@ -14616,10 +14674,10 @@
         <v>411</v>
       </c>
       <c r="B721">
-        <v>41100431</v>
+        <v>41100429</v>
       </c>
       <c r="C721" t="s">
-        <v>116</v>
+        <v>394</v>
       </c>
     </row>
     <row r="722" spans="1:3" x14ac:dyDescent="0.25">
@@ -14627,10 +14685,10 @@
         <v>411</v>
       </c>
       <c r="B722">
-        <v>41100432</v>
+        <v>4110043</v>
       </c>
       <c r="C722" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="723" spans="1:3" x14ac:dyDescent="0.25">
@@ -14638,10 +14696,10 @@
         <v>411</v>
       </c>
       <c r="B723">
-        <v>41100433</v>
+        <v>41100430</v>
       </c>
       <c r="C723" t="s">
-        <v>5</v>
+        <v>396</v>
       </c>
     </row>
     <row r="724" spans="1:3" x14ac:dyDescent="0.25">
@@ -14649,10 +14707,10 @@
         <v>411</v>
       </c>
       <c r="B724">
-        <v>41100439</v>
+        <v>41100431</v>
       </c>
       <c r="C724" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.25">
@@ -14660,10 +14718,10 @@
         <v>411</v>
       </c>
       <c r="B725">
-        <v>41100440</v>
+        <v>41100432</v>
       </c>
       <c r="C725" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.25">
@@ -14671,10 +14729,10 @@
         <v>411</v>
       </c>
       <c r="B726">
-        <v>41100441</v>
+        <v>41100433</v>
       </c>
       <c r="C726" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.25">
@@ -14682,10 +14740,10 @@
         <v>411</v>
       </c>
       <c r="B727">
-        <v>41100442</v>
+        <v>41100439</v>
       </c>
       <c r="C727" t="s">
-        <v>142</v>
+        <v>77</v>
       </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.25">
@@ -14693,10 +14751,10 @@
         <v>411</v>
       </c>
       <c r="B728">
-        <v>41100443</v>
+        <v>41100440</v>
       </c>
       <c r="C728" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="729" spans="1:3" x14ac:dyDescent="0.25">
@@ -14704,10 +14762,10 @@
         <v>411</v>
       </c>
       <c r="B729">
-        <v>41100444</v>
+        <v>41100441</v>
       </c>
       <c r="C729" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
     </row>
     <row r="730" spans="1:3" x14ac:dyDescent="0.25">
@@ -14715,10 +14773,10 @@
         <v>411</v>
       </c>
       <c r="B730">
-        <v>4110045</v>
+        <v>41100442</v>
       </c>
       <c r="C730" t="s">
-        <v>400</v>
+        <v>142</v>
       </c>
     </row>
     <row r="731" spans="1:3" x14ac:dyDescent="0.25">
@@ -14726,10 +14784,10 @@
         <v>411</v>
       </c>
       <c r="B731">
-        <v>41100485</v>
+        <v>41100443</v>
       </c>
       <c r="C731" t="s">
-        <v>70</v>
+        <v>399</v>
       </c>
     </row>
     <row r="732" spans="1:3" x14ac:dyDescent="0.25">
@@ -14737,10 +14795,10 @@
         <v>411</v>
       </c>
       <c r="B732">
-        <v>41100486</v>
+        <v>41100444</v>
       </c>
       <c r="C732" t="s">
-        <v>45</v>
+        <v>147</v>
       </c>
     </row>
     <row r="733" spans="1:3" x14ac:dyDescent="0.25">
@@ -14748,10 +14806,10 @@
         <v>411</v>
       </c>
       <c r="B733">
-        <v>41100487</v>
+        <v>4110045</v>
       </c>
       <c r="C733" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="734" spans="1:3" x14ac:dyDescent="0.25">
@@ -14759,10 +14817,10 @@
         <v>411</v>
       </c>
       <c r="B734">
-        <v>41100488</v>
+        <v>41100485</v>
       </c>
       <c r="C734" t="s">
-        <v>402</v>
+        <v>70</v>
       </c>
     </row>
     <row r="735" spans="1:3" x14ac:dyDescent="0.25">
@@ -14770,10 +14828,10 @@
         <v>411</v>
       </c>
       <c r="B735">
-        <v>41100489</v>
+        <v>41100486</v>
       </c>
       <c r="C735" t="s">
-        <v>403</v>
+        <v>45</v>
       </c>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.25">
@@ -14781,10 +14839,10 @@
         <v>411</v>
       </c>
       <c r="B736">
-        <v>4110049</v>
+        <v>41100487</v>
       </c>
       <c r="C736" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.25">
@@ -14792,10 +14850,10 @@
         <v>411</v>
       </c>
       <c r="B737">
-        <v>41100490</v>
+        <v>41100488</v>
       </c>
       <c r="C737" t="s">
-        <v>74</v>
+        <v>402</v>
       </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.25">
@@ -14803,10 +14861,10 @@
         <v>411</v>
       </c>
       <c r="B738">
-        <v>41100491</v>
+        <v>41100489</v>
       </c>
       <c r="C738" t="s">
-        <v>24</v>
+        <v>403</v>
       </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.25">
@@ -14814,10 +14872,10 @@
         <v>411</v>
       </c>
       <c r="B739">
-        <v>41100492</v>
+        <v>4110049</v>
       </c>
       <c r="C739" t="s">
-        <v>20</v>
+        <v>404</v>
       </c>
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.25">
@@ -14825,10 +14883,10 @@
         <v>411</v>
       </c>
       <c r="B740">
-        <v>41100493</v>
+        <v>41100490</v>
       </c>
       <c r="C740" t="s">
-        <v>405</v>
+        <v>74</v>
       </c>
     </row>
     <row r="741" spans="1:3" x14ac:dyDescent="0.25">
@@ -14836,10 +14894,10 @@
         <v>411</v>
       </c>
       <c r="B741">
-        <v>41100494</v>
+        <v>41100491</v>
       </c>
       <c r="C741" t="s">
-        <v>406</v>
+        <v>24</v>
       </c>
     </row>
     <row r="742" spans="1:3" x14ac:dyDescent="0.25">
@@ -14847,10 +14905,10 @@
         <v>411</v>
       </c>
       <c r="B742">
-        <v>41100495</v>
+        <v>41100492</v>
       </c>
       <c r="C742" t="s">
-        <v>407</v>
+        <v>20</v>
       </c>
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.25">
@@ -14858,10 +14916,10 @@
         <v>411</v>
       </c>
       <c r="B743">
-        <v>41100496</v>
+        <v>41100493</v>
       </c>
       <c r="C743" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="744" spans="1:3" x14ac:dyDescent="0.25">
@@ -14869,10 +14927,10 @@
         <v>411</v>
       </c>
       <c r="B744">
-        <v>41100497</v>
+        <v>41100494</v>
       </c>
       <c r="C744" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="745" spans="1:3" x14ac:dyDescent="0.25">
@@ -14880,10 +14938,10 @@
         <v>411</v>
       </c>
       <c r="B745">
-        <v>41100498</v>
+        <v>41100495</v>
       </c>
       <c r="C745" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="746" spans="1:3" x14ac:dyDescent="0.25">
@@ -14891,10 +14949,10 @@
         <v>411</v>
       </c>
       <c r="B746">
-        <v>41100499</v>
+        <v>41100496</v>
       </c>
       <c r="C746" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.25">
@@ -14902,10 +14960,10 @@
         <v>411</v>
       </c>
       <c r="B747">
-        <v>411005</v>
+        <v>41100497</v>
       </c>
       <c r="C747" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.25">
@@ -14913,10 +14971,10 @@
         <v>411</v>
       </c>
       <c r="B748">
-        <v>41100500</v>
+        <v>41100498</v>
       </c>
       <c r="C748" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.25">
@@ -14924,10 +14982,10 @@
         <v>411</v>
       </c>
       <c r="B749">
-        <v>4110061</v>
+        <v>41100499</v>
       </c>
       <c r="C749" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.25">
@@ -14935,10 +14993,10 @@
         <v>411</v>
       </c>
       <c r="B750">
-        <v>41100610</v>
+        <v>411005</v>
       </c>
       <c r="C750" t="s">
-        <v>66</v>
+        <v>412</v>
       </c>
     </row>
     <row r="751" spans="1:3" x14ac:dyDescent="0.25">
@@ -14946,10 +15004,10 @@
         <v>411</v>
       </c>
       <c r="B751">
-        <v>41100611</v>
+        <v>41100500</v>
       </c>
       <c r="C751" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="752" spans="1:3" x14ac:dyDescent="0.25">
@@ -14957,10 +15015,10 @@
         <v>411</v>
       </c>
       <c r="B752">
-        <v>41100612</v>
+        <v>4110061</v>
       </c>
       <c r="C752" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="753" spans="1:3" x14ac:dyDescent="0.25">
@@ -14968,10 +15026,10 @@
         <v>411</v>
       </c>
       <c r="B753">
-        <v>41100613</v>
+        <v>41100610</v>
       </c>
       <c r="C753" t="s">
-        <v>417</v>
+        <v>66</v>
       </c>
     </row>
     <row r="754" spans="1:3" x14ac:dyDescent="0.25">
@@ -14979,10 +15037,10 @@
         <v>411</v>
       </c>
       <c r="B754">
-        <v>41100614</v>
+        <v>41100611</v>
       </c>
       <c r="C754" t="s">
-        <v>94</v>
+        <v>415</v>
       </c>
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.25">
@@ -14990,10 +15048,10 @@
         <v>411</v>
       </c>
       <c r="B755">
-        <v>41100615</v>
+        <v>41100612</v>
       </c>
       <c r="C755" t="s">
-        <v>63</v>
+        <v>416</v>
       </c>
     </row>
     <row r="756" spans="1:3" x14ac:dyDescent="0.25">
@@ -15001,10 +15059,10 @@
         <v>411</v>
       </c>
       <c r="B756">
-        <v>41100616</v>
+        <v>41100613</v>
       </c>
       <c r="C756" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="757" spans="1:3" x14ac:dyDescent="0.25">
@@ -15012,10 +15070,10 @@
         <v>411</v>
       </c>
       <c r="B757">
-        <v>41100617</v>
+        <v>41100614</v>
       </c>
       <c r="C757" t="s">
-        <v>419</v>
+        <v>94</v>
       </c>
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.25">
@@ -15023,10 +15081,10 @@
         <v>411</v>
       </c>
       <c r="B758">
-        <v>41100618</v>
+        <v>41100615</v>
       </c>
       <c r="C758" t="s">
-        <v>420</v>
+        <v>63</v>
       </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.25">
@@ -15034,10 +15092,10 @@
         <v>411</v>
       </c>
       <c r="B759">
-        <v>41100619</v>
+        <v>41100616</v>
       </c>
       <c r="C759" t="s">
-        <v>76</v>
+        <v>418</v>
       </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.25">
@@ -15045,10 +15103,10 @@
         <v>411</v>
       </c>
       <c r="B760">
-        <v>41100620</v>
+        <v>41100617</v>
       </c>
       <c r="C760" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.25">
@@ -15056,10 +15114,10 @@
         <v>411</v>
       </c>
       <c r="B761">
-        <v>41100621</v>
+        <v>41100618</v>
       </c>
       <c r="C761" t="s">
-        <v>27</v>
+        <v>420</v>
       </c>
     </row>
     <row r="762" spans="1:3" x14ac:dyDescent="0.25">
@@ -15067,10 +15125,10 @@
         <v>411</v>
       </c>
       <c r="B762">
-        <v>41100622</v>
+        <v>41100619</v>
       </c>
       <c r="C762" t="s">
-        <v>422</v>
+        <v>76</v>
       </c>
     </row>
     <row r="763" spans="1:3" x14ac:dyDescent="0.25">
@@ -15078,10 +15136,10 @@
         <v>411</v>
       </c>
       <c r="B763">
-        <v>41100623</v>
+        <v>41100620</v>
       </c>
       <c r="C763" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.25">
@@ -15089,10 +15147,10 @@
         <v>411</v>
       </c>
       <c r="B764">
-        <v>41100624</v>
+        <v>41100621</v>
       </c>
       <c r="C764" t="s">
-        <v>424</v>
+        <v>27</v>
       </c>
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.25">
@@ -15100,10 +15158,10 @@
         <v>411</v>
       </c>
       <c r="B765">
-        <v>41100625</v>
+        <v>41100622</v>
       </c>
       <c r="C765" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.25">
@@ -15111,10 +15169,10 @@
         <v>411</v>
       </c>
       <c r="B766">
-        <v>41100626</v>
+        <v>41100623</v>
       </c>
       <c r="C766" t="s">
-        <v>48</v>
+        <v>423</v>
       </c>
     </row>
     <row r="767" spans="1:3" x14ac:dyDescent="0.25">
@@ -15122,10 +15180,10 @@
         <v>411</v>
       </c>
       <c r="B767">
-        <v>41100627</v>
+        <v>41100624</v>
       </c>
       <c r="C767" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="768" spans="1:3" x14ac:dyDescent="0.25">
@@ -15133,10 +15191,10 @@
         <v>411</v>
       </c>
       <c r="B768">
-        <v>41100628</v>
+        <v>41100625</v>
       </c>
       <c r="C768" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.25">
@@ -15144,10 +15202,10 @@
         <v>411</v>
       </c>
       <c r="B769">
-        <v>41100629</v>
+        <v>41100626</v>
       </c>
       <c r="C769" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.25">
@@ -15155,10 +15213,10 @@
         <v>411</v>
       </c>
       <c r="B770">
-        <v>41100630</v>
+        <v>41100627</v>
       </c>
       <c r="C770" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.25">
@@ -15166,10 +15224,10 @@
         <v>411</v>
       </c>
       <c r="B771">
-        <v>41100631</v>
+        <v>41100628</v>
       </c>
       <c r="C771" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.25">
@@ -15177,10 +15235,10 @@
         <v>411</v>
       </c>
       <c r="B772">
-        <v>41100632</v>
+        <v>41100629</v>
       </c>
       <c r="C772" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
     </row>
     <row r="773" spans="1:3" x14ac:dyDescent="0.25">
@@ -15188,10 +15246,10 @@
         <v>411</v>
       </c>
       <c r="B773">
-        <v>41100633</v>
+        <v>41100630</v>
       </c>
       <c r="C773" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="774" spans="1:3" x14ac:dyDescent="0.25">
@@ -15199,10 +15257,10 @@
         <v>411</v>
       </c>
       <c r="B774">
-        <v>41100634</v>
+        <v>41100631</v>
       </c>
       <c r="C774" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="775" spans="1:3" x14ac:dyDescent="0.25">
@@ -15210,10 +15268,10 @@
         <v>411</v>
       </c>
       <c r="B775">
-        <v>41100635</v>
+        <v>41100632</v>
       </c>
       <c r="C775" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="776" spans="1:3" x14ac:dyDescent="0.25">
@@ -15221,10 +15279,10 @@
         <v>411</v>
       </c>
       <c r="B776">
-        <v>41100636</v>
+        <v>41100633</v>
       </c>
       <c r="C776" t="s">
-        <v>51</v>
+        <v>430</v>
       </c>
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.25">
@@ -15232,10 +15290,10 @@
         <v>411</v>
       </c>
       <c r="B777">
-        <v>41100637</v>
+        <v>41100634</v>
       </c>
       <c r="C777" t="s">
-        <v>7</v>
+        <v>431</v>
       </c>
     </row>
     <row r="778" spans="1:3" x14ac:dyDescent="0.25">
@@ -15243,10 +15301,10 @@
         <v>411</v>
       </c>
       <c r="B778">
-        <v>41100638</v>
+        <v>41100635</v>
       </c>
       <c r="C778" t="s">
-        <v>432</v>
+        <v>32</v>
       </c>
     </row>
     <row r="779" spans="1:3" x14ac:dyDescent="0.25">
@@ -15254,10 +15312,10 @@
         <v>411</v>
       </c>
       <c r="B779">
-        <v>41100639</v>
+        <v>41100636</v>
       </c>
       <c r="C779" t="s">
-        <v>433</v>
+        <v>51</v>
       </c>
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.25">
@@ -15265,10 +15323,10 @@
         <v>411</v>
       </c>
       <c r="B780">
-        <v>4110064</v>
+        <v>41100637</v>
       </c>
       <c r="C780" t="s">
-        <v>434</v>
+        <v>7</v>
       </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.25">
@@ -15276,10 +15334,10 @@
         <v>411</v>
       </c>
       <c r="B781">
-        <v>41100640</v>
+        <v>41100638</v>
       </c>
       <c r="C781" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.25">
@@ -15287,10 +15345,10 @@
         <v>411</v>
       </c>
       <c r="B782">
-        <v>41100641</v>
+        <v>41100639</v>
       </c>
       <c r="C782" t="s">
-        <v>71</v>
+        <v>433</v>
       </c>
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.25">
@@ -15298,10 +15356,10 @@
         <v>411</v>
       </c>
       <c r="B783">
-        <v>41100642</v>
+        <v>4110064</v>
       </c>
       <c r="C783" t="s">
-        <v>50</v>
+        <v>434</v>
       </c>
     </row>
     <row r="784" spans="1:3" x14ac:dyDescent="0.25">
@@ -15309,10 +15367,10 @@
         <v>411</v>
       </c>
       <c r="B784">
-        <v>41100643</v>
+        <v>41100640</v>
       </c>
       <c r="C784" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="785" spans="1:3" x14ac:dyDescent="0.25">
@@ -15320,10 +15378,10 @@
         <v>411</v>
       </c>
       <c r="B785">
-        <v>41100644</v>
+        <v>41100641</v>
       </c>
       <c r="C785" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
     </row>
     <row r="786" spans="1:3" x14ac:dyDescent="0.25">
@@ -15331,10 +15389,10 @@
         <v>411</v>
       </c>
       <c r="B786">
-        <v>41100645</v>
+        <v>41100642</v>
       </c>
       <c r="C786" t="s">
-        <v>437</v>
+        <v>50</v>
       </c>
     </row>
     <row r="787" spans="1:3" x14ac:dyDescent="0.25">
@@ -15342,10 +15400,10 @@
         <v>411</v>
       </c>
       <c r="B787">
-        <v>41100646</v>
+        <v>41100643</v>
       </c>
       <c r="C787" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="788" spans="1:3" x14ac:dyDescent="0.25">
@@ -15353,10 +15411,10 @@
         <v>411</v>
       </c>
       <c r="B788">
-        <v>41100647</v>
+        <v>41100644</v>
       </c>
       <c r="C788" t="s">
-        <v>439</v>
+        <v>47</v>
       </c>
     </row>
     <row r="789" spans="1:3" x14ac:dyDescent="0.25">
@@ -15364,10 +15422,10 @@
         <v>411</v>
       </c>
       <c r="B789">
-        <v>41100648</v>
+        <v>41100645</v>
       </c>
       <c r="C789" t="s">
-        <v>10</v>
+        <v>437</v>
       </c>
     </row>
     <row r="790" spans="1:3" x14ac:dyDescent="0.25">
@@ -15375,10 +15433,10 @@
         <v>411</v>
       </c>
       <c r="B790">
-        <v>41100649</v>
+        <v>41100646</v>
       </c>
       <c r="C790" t="s">
-        <v>59</v>
+        <v>438</v>
       </c>
     </row>
     <row r="791" spans="1:3" x14ac:dyDescent="0.25">
@@ -15386,10 +15444,10 @@
         <v>411</v>
       </c>
       <c r="B791">
-        <v>41100650</v>
+        <v>41100647</v>
       </c>
       <c r="C791" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.25">
@@ -15397,10 +15455,10 @@
         <v>411</v>
       </c>
       <c r="B792">
-        <v>41100651</v>
+        <v>41100648</v>
       </c>
       <c r="C792" t="s">
-        <v>441</v>
+        <v>10</v>
       </c>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.25">
@@ -15408,10 +15466,10 @@
         <v>411</v>
       </c>
       <c r="B793">
-        <v>41100652</v>
+        <v>41100649</v>
       </c>
       <c r="C793" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.25">
@@ -15419,10 +15477,10 @@
         <v>411</v>
       </c>
       <c r="B794">
-        <v>41100653</v>
+        <v>41100650</v>
       </c>
       <c r="C794" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="795" spans="1:3" x14ac:dyDescent="0.25">
@@ -15430,10 +15488,10 @@
         <v>411</v>
       </c>
       <c r="B795">
-        <v>41100654</v>
+        <v>41100651</v>
       </c>
       <c r="C795" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="796" spans="1:3" x14ac:dyDescent="0.25">
@@ -15441,10 +15499,10 @@
         <v>411</v>
       </c>
       <c r="B796">
-        <v>41100655</v>
+        <v>41100652</v>
       </c>
       <c r="C796" t="s">
-        <v>444</v>
+        <v>37</v>
       </c>
     </row>
     <row r="797" spans="1:3" x14ac:dyDescent="0.25">
@@ -15452,10 +15510,10 @@
         <v>411</v>
       </c>
       <c r="B797">
-        <v>41100656</v>
+        <v>41100653</v>
       </c>
       <c r="C797" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="798" spans="1:3" x14ac:dyDescent="0.25">
@@ -15463,10 +15521,10 @@
         <v>411</v>
       </c>
       <c r="B798">
-        <v>41100657</v>
+        <v>41100654</v>
       </c>
       <c r="C798" t="s">
-        <v>19</v>
+        <v>443</v>
       </c>
     </row>
     <row r="799" spans="1:3" x14ac:dyDescent="0.25">
@@ -15474,10 +15532,10 @@
         <v>411</v>
       </c>
       <c r="B799">
-        <v>41100658</v>
+        <v>41100655</v>
       </c>
       <c r="C799" t="s">
-        <v>38</v>
+        <v>444</v>
       </c>
     </row>
     <row r="800" spans="1:3" x14ac:dyDescent="0.25">
@@ -15485,10 +15543,10 @@
         <v>411</v>
       </c>
       <c r="B800">
-        <v>41100659</v>
+        <v>41100656</v>
       </c>
       <c r="C800" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="801" spans="1:3" x14ac:dyDescent="0.25">
@@ -15496,10 +15554,10 @@
         <v>411</v>
       </c>
       <c r="B801">
-        <v>4110066</v>
+        <v>41100657</v>
       </c>
       <c r="C801" t="s">
-        <v>447</v>
+        <v>19</v>
       </c>
     </row>
     <row r="802" spans="1:3" x14ac:dyDescent="0.25">
@@ -15507,10 +15565,10 @@
         <v>411</v>
       </c>
       <c r="B802">
-        <v>41100660</v>
+        <v>41100658</v>
       </c>
       <c r="C802" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.25">
@@ -15518,10 +15576,10 @@
         <v>411</v>
       </c>
       <c r="B803">
-        <v>41100661</v>
+        <v>41100659</v>
       </c>
       <c r="C803" t="s">
-        <v>52</v>
+        <v>446</v>
       </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.25">
@@ -15529,10 +15587,10 @@
         <v>411</v>
       </c>
       <c r="B804">
-        <v>41100662</v>
+        <v>4110066</v>
       </c>
       <c r="C804" t="s">
-        <v>56</v>
+        <v>447</v>
       </c>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.25">
@@ -15540,10 +15598,10 @@
         <v>411</v>
       </c>
       <c r="B805">
-        <v>41100663</v>
+        <v>41100660</v>
       </c>
       <c r="C805" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
     </row>
     <row r="806" spans="1:3" x14ac:dyDescent="0.25">
@@ -15551,10 +15609,10 @@
         <v>411</v>
       </c>
       <c r="B806">
-        <v>41100664</v>
+        <v>41100661</v>
       </c>
       <c r="C806" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="807" spans="1:3" x14ac:dyDescent="0.25">
@@ -15562,10 +15620,10 @@
         <v>411</v>
       </c>
       <c r="B807">
-        <v>41100665</v>
+        <v>41100662</v>
       </c>
       <c r="C807" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="808" spans="1:3" x14ac:dyDescent="0.25">
@@ -15573,10 +15631,10 @@
         <v>411</v>
       </c>
       <c r="B808">
-        <v>41100666</v>
+        <v>41100663</v>
       </c>
       <c r="C808" t="s">
-        <v>448</v>
+        <v>30</v>
       </c>
     </row>
     <row r="809" spans="1:3" x14ac:dyDescent="0.25">
@@ -15584,10 +15642,10 @@
         <v>411</v>
       </c>
       <c r="B809">
-        <v>41100667</v>
+        <v>41100664</v>
       </c>
       <c r="C809" t="s">
-        <v>449</v>
+        <v>53</v>
       </c>
     </row>
     <row r="810" spans="1:3" x14ac:dyDescent="0.25">
@@ -15595,10 +15653,10 @@
         <v>411</v>
       </c>
       <c r="B810">
-        <v>41100668</v>
+        <v>41100665</v>
       </c>
       <c r="C810" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
     </row>
     <row r="811" spans="1:3" x14ac:dyDescent="0.25">
@@ -15606,10 +15664,10 @@
         <v>411</v>
       </c>
       <c r="B811">
-        <v>41100669</v>
+        <v>41100666</v>
       </c>
       <c r="C811" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="812" spans="1:3" x14ac:dyDescent="0.25">
@@ -15617,10 +15675,10 @@
         <v>411</v>
       </c>
       <c r="B812">
-        <v>4110067</v>
+        <v>41100667</v>
       </c>
       <c r="C812" t="s">
-        <v>748</v>
+        <v>449</v>
       </c>
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.25">
@@ -15628,10 +15686,10 @@
         <v>411</v>
       </c>
       <c r="B813">
-        <v>41100670</v>
+        <v>41100668</v>
       </c>
       <c r="C813" t="s">
-        <v>451</v>
+        <v>109</v>
       </c>
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.25">
@@ -15639,10 +15697,10 @@
         <v>411</v>
       </c>
       <c r="B814">
-        <v>41100671</v>
+        <v>41100669</v>
       </c>
       <c r="C814" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.25">
@@ -15650,10 +15708,10 @@
         <v>411</v>
       </c>
       <c r="B815">
-        <v>41100673</v>
+        <v>4110067</v>
       </c>
       <c r="C815" t="s">
-        <v>33</v>
+        <v>748</v>
       </c>
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.25">
@@ -15661,10 +15719,10 @@
         <v>411</v>
       </c>
       <c r="B816">
-        <v>41100674</v>
+        <v>41100670</v>
       </c>
       <c r="C816" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="817" spans="1:3" x14ac:dyDescent="0.25">
@@ -15672,10 +15730,10 @@
         <v>411</v>
       </c>
       <c r="B817">
-        <v>41100675</v>
+        <v>41100671</v>
       </c>
       <c r="C817" t="s">
-        <v>60</v>
+        <v>452</v>
       </c>
     </row>
     <row r="818" spans="1:3" x14ac:dyDescent="0.25">
@@ -15683,10 +15741,10 @@
         <v>411</v>
       </c>
       <c r="B818">
-        <v>41100676</v>
+        <v>41100673</v>
       </c>
       <c r="C818" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="819" spans="1:3" x14ac:dyDescent="0.25">
@@ -15694,10 +15752,10 @@
         <v>411</v>
       </c>
       <c r="B819">
-        <v>4110069</v>
+        <v>41100674</v>
       </c>
       <c r="C819" t="s">
-        <v>255</v>
+        <v>453</v>
       </c>
     </row>
     <row r="820" spans="1:3" x14ac:dyDescent="0.25">
@@ -15705,10 +15763,10 @@
         <v>411</v>
       </c>
       <c r="B820">
-        <v>4110071</v>
+        <v>41100675</v>
       </c>
       <c r="C820" t="s">
-        <v>213</v>
+        <v>60</v>
       </c>
     </row>
     <row r="821" spans="1:3" x14ac:dyDescent="0.25">
@@ -15716,10 +15774,10 @@
         <v>411</v>
       </c>
       <c r="B821">
-        <v>4110072</v>
+        <v>41100676</v>
       </c>
       <c r="C821" t="s">
-        <v>454</v>
+        <v>6</v>
       </c>
     </row>
     <row r="822" spans="1:3" x14ac:dyDescent="0.25">
@@ -15727,10 +15785,10 @@
         <v>411</v>
       </c>
       <c r="B822">
-        <v>4110073</v>
+        <v>4110069</v>
       </c>
       <c r="C822" t="s">
-        <v>455</v>
+        <v>255</v>
       </c>
     </row>
     <row r="823" spans="1:3" x14ac:dyDescent="0.25">
@@ -15738,10 +15796,10 @@
         <v>411</v>
       </c>
       <c r="B823">
-        <v>41100730</v>
+        <v>4110071</v>
       </c>
       <c r="C823" t="s">
-        <v>456</v>
+        <v>213</v>
       </c>
     </row>
     <row r="824" spans="1:3" x14ac:dyDescent="0.25">
@@ -15749,10 +15807,10 @@
         <v>411</v>
       </c>
       <c r="B824">
-        <v>41100731</v>
+        <v>4110072</v>
       </c>
       <c r="C824" t="s">
-        <v>62</v>
+        <v>454</v>
       </c>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.25">
@@ -15760,10 +15818,10 @@
         <v>411</v>
       </c>
       <c r="B825">
-        <v>41100732</v>
+        <v>4110073</v>
       </c>
       <c r="C825" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.25">
@@ -15771,10 +15829,10 @@
         <v>411</v>
       </c>
       <c r="B826">
-        <v>41100733</v>
+        <v>41100730</v>
       </c>
       <c r="C826" t="s">
-        <v>25</v>
+        <v>456</v>
       </c>
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.25">
@@ -15782,10 +15840,10 @@
         <v>411</v>
       </c>
       <c r="B827">
-        <v>41100734</v>
+        <v>41100731</v>
       </c>
       <c r="C827" t="s">
-        <v>458</v>
+        <v>62</v>
       </c>
     </row>
     <row r="828" spans="1:3" x14ac:dyDescent="0.25">
@@ -15793,10 +15851,10 @@
         <v>411</v>
       </c>
       <c r="B828">
-        <v>41100735</v>
+        <v>41100732</v>
       </c>
       <c r="C828" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="829" spans="1:3" x14ac:dyDescent="0.25">
@@ -15804,10 +15862,10 @@
         <v>411</v>
       </c>
       <c r="B829">
-        <v>41100736</v>
+        <v>41100733</v>
       </c>
       <c r="C829" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="830" spans="1:3" x14ac:dyDescent="0.25">
@@ -15815,10 +15873,10 @@
         <v>411</v>
       </c>
       <c r="B830">
-        <v>41100737</v>
+        <v>41100734</v>
       </c>
       <c r="C830" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="831" spans="1:3" x14ac:dyDescent="0.25">
@@ -15826,10 +15884,10 @@
         <v>411</v>
       </c>
       <c r="B831">
-        <v>41100738</v>
+        <v>41100735</v>
       </c>
       <c r="C831" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="832" spans="1:3" x14ac:dyDescent="0.25">
@@ -15837,10 +15895,10 @@
         <v>411</v>
       </c>
       <c r="B832">
-        <v>41100739</v>
+        <v>41100736</v>
       </c>
       <c r="C832" t="s">
-        <v>462</v>
+        <v>43</v>
       </c>
     </row>
     <row r="833" spans="1:3" x14ac:dyDescent="0.25">
@@ -15848,10 +15906,10 @@
         <v>411</v>
       </c>
       <c r="B833">
-        <v>41100740</v>
+        <v>41100737</v>
       </c>
       <c r="C833" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="834" spans="1:3" x14ac:dyDescent="0.25">
@@ -15859,10 +15917,10 @@
         <v>411</v>
       </c>
       <c r="B834">
-        <v>41100741</v>
+        <v>41100738</v>
       </c>
       <c r="C834" t="s">
-        <v>12</v>
+        <v>461</v>
       </c>
     </row>
     <row r="835" spans="1:3" x14ac:dyDescent="0.25">
@@ -15870,10 +15928,10 @@
         <v>411</v>
       </c>
       <c r="B835">
-        <v>41100742</v>
+        <v>41100739</v>
       </c>
       <c r="C835" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.25">
@@ -15881,10 +15939,10 @@
         <v>411</v>
       </c>
       <c r="B836">
-        <v>41100743</v>
+        <v>41100740</v>
       </c>
       <c r="C836" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.25">
@@ -15892,10 +15950,10 @@
         <v>411</v>
       </c>
       <c r="B837">
-        <v>41100744</v>
+        <v>41100741</v>
       </c>
       <c r="C837" t="s">
-        <v>466</v>
+        <v>12</v>
       </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.25">
@@ -15903,10 +15961,10 @@
         <v>411</v>
       </c>
       <c r="B838">
-        <v>41100745</v>
+        <v>41100742</v>
       </c>
       <c r="C838" t="s">
-        <v>3</v>
+        <v>464</v>
       </c>
     </row>
     <row r="839" spans="1:3" x14ac:dyDescent="0.25">
@@ -15914,10 +15972,10 @@
         <v>411</v>
       </c>
       <c r="B839">
-        <v>41100746</v>
+        <v>41100743</v>
       </c>
       <c r="C839" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="840" spans="1:3" x14ac:dyDescent="0.25">
@@ -15925,10 +15983,10 @@
         <v>411</v>
       </c>
       <c r="B840">
-        <v>41100747</v>
+        <v>41100744</v>
       </c>
       <c r="C840" t="s">
-        <v>46</v>
+        <v>466</v>
       </c>
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.25">
@@ -15936,10 +15994,10 @@
         <v>411</v>
       </c>
       <c r="B841">
-        <v>41100748</v>
+        <v>41100745</v>
       </c>
       <c r="C841" t="s">
-        <v>468</v>
+        <v>3</v>
       </c>
     </row>
     <row r="842" spans="1:3" x14ac:dyDescent="0.25">
@@ -15947,10 +16005,10 @@
         <v>411</v>
       </c>
       <c r="B842">
-        <v>41100749</v>
+        <v>41100746</v>
       </c>
       <c r="C842" t="s">
-        <v>54</v>
+        <v>467</v>
       </c>
     </row>
     <row r="843" spans="1:3" x14ac:dyDescent="0.25">
@@ -15958,10 +16016,10 @@
         <v>411</v>
       </c>
       <c r="B843">
-        <v>4110075</v>
+        <v>41100747</v>
       </c>
       <c r="C843" t="s">
-        <v>469</v>
+        <v>46</v>
       </c>
     </row>
     <row r="844" spans="1:3" x14ac:dyDescent="0.25">
@@ -15969,10 +16027,10 @@
         <v>411</v>
       </c>
       <c r="B844">
-        <v>41100750</v>
+        <v>41100748</v>
       </c>
       <c r="C844" t="s">
-        <v>4</v>
+        <v>468</v>
       </c>
     </row>
     <row r="845" spans="1:3" x14ac:dyDescent="0.25">
@@ -15980,10 +16038,10 @@
         <v>411</v>
       </c>
       <c r="B845">
-        <v>41100751</v>
+        <v>41100749</v>
       </c>
       <c r="C845" t="s">
-        <v>470</v>
+        <v>54</v>
       </c>
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.25">
@@ -15991,10 +16049,10 @@
         <v>411</v>
       </c>
       <c r="B846">
-        <v>41100752</v>
+        <v>4110075</v>
       </c>
       <c r="C846" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.25">
@@ -16002,10 +16060,10 @@
         <v>411</v>
       </c>
       <c r="B847">
-        <v>41100753</v>
+        <v>41100750</v>
       </c>
       <c r="C847" t="s">
-        <v>472</v>
+        <v>4</v>
       </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.25">
@@ -16013,10 +16071,10 @@
         <v>411</v>
       </c>
       <c r="B848">
-        <v>41100754</v>
+        <v>41100751</v>
       </c>
       <c r="C848" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.25">
@@ -16024,10 +16082,10 @@
         <v>411</v>
       </c>
       <c r="B849">
-        <v>41100755</v>
+        <v>41100752</v>
       </c>
       <c r="C849" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="850" spans="1:3" x14ac:dyDescent="0.25">
@@ -16035,10 +16093,10 @@
         <v>411</v>
       </c>
       <c r="B850">
-        <v>41100756</v>
+        <v>41100753</v>
       </c>
       <c r="C850" t="s">
-        <v>9</v>
+        <v>472</v>
       </c>
     </row>
     <row r="851" spans="1:3" x14ac:dyDescent="0.25">
@@ -16046,10 +16104,10 @@
         <v>411</v>
       </c>
       <c r="B851">
-        <v>41100757</v>
+        <v>41100754</v>
       </c>
       <c r="C851" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="852" spans="1:3" x14ac:dyDescent="0.25">
@@ -16057,10 +16115,10 @@
         <v>411</v>
       </c>
       <c r="B852">
-        <v>41100758</v>
+        <v>41100755</v>
       </c>
       <c r="C852" t="s">
-        <v>356</v>
+        <v>474</v>
       </c>
     </row>
     <row r="853" spans="1:3" x14ac:dyDescent="0.25">
@@ -16068,10 +16126,10 @@
         <v>411</v>
       </c>
       <c r="B853">
-        <v>41100759</v>
+        <v>41100756</v>
       </c>
       <c r="C853" t="s">
-        <v>476</v>
+        <v>9</v>
       </c>
     </row>
     <row r="854" spans="1:3" x14ac:dyDescent="0.25">
@@ -16079,10 +16137,10 @@
         <v>411</v>
       </c>
       <c r="B854">
-        <v>4110076</v>
+        <v>41100757</v>
       </c>
       <c r="C854" t="s">
-        <v>207</v>
+        <v>475</v>
       </c>
     </row>
     <row r="855" spans="1:3" x14ac:dyDescent="0.25">
@@ -16090,10 +16148,10 @@
         <v>411</v>
       </c>
       <c r="B855">
-        <v>41100760</v>
+        <v>41100758</v>
       </c>
       <c r="C855" t="s">
-        <v>477</v>
+        <v>356</v>
       </c>
     </row>
     <row r="856" spans="1:3" x14ac:dyDescent="0.25">
@@ -16101,10 +16159,10 @@
         <v>411</v>
       </c>
       <c r="B856">
-        <v>41100761</v>
+        <v>41100759</v>
       </c>
       <c r="C856" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="857" spans="1:3" x14ac:dyDescent="0.25">
@@ -16112,10 +16170,10 @@
         <v>411</v>
       </c>
       <c r="B857">
-        <v>41100762</v>
+        <v>4110076</v>
       </c>
       <c r="C857" t="s">
-        <v>479</v>
+        <v>207</v>
       </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.25">
@@ -16123,10 +16181,10 @@
         <v>411</v>
       </c>
       <c r="B858">
-        <v>41100763</v>
+        <v>41100760</v>
       </c>
       <c r="C858" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.25">
@@ -16134,10 +16192,10 @@
         <v>411</v>
       </c>
       <c r="B859">
-        <v>41100764</v>
+        <v>41100761</v>
       </c>
       <c r="C859" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.25">
@@ -16145,10 +16203,10 @@
         <v>411</v>
       </c>
       <c r="B860">
-        <v>41100765</v>
+        <v>41100762</v>
       </c>
       <c r="C860" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="861" spans="1:3" x14ac:dyDescent="0.25">
@@ -16156,10 +16214,10 @@
         <v>411</v>
       </c>
       <c r="B861">
-        <v>41100766</v>
+        <v>41100763</v>
       </c>
       <c r="C861" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="862" spans="1:3" x14ac:dyDescent="0.25">
@@ -16167,10 +16225,10 @@
         <v>411</v>
       </c>
       <c r="B862">
-        <v>41100767</v>
+        <v>41100764</v>
       </c>
       <c r="C862" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="863" spans="1:3" x14ac:dyDescent="0.25">
@@ -16178,10 +16236,10 @@
         <v>411</v>
       </c>
       <c r="B863">
-        <v>41100768</v>
+        <v>41100765</v>
       </c>
       <c r="C863" t="s">
-        <v>29</v>
+        <v>482</v>
       </c>
     </row>
     <row r="864" spans="1:3" x14ac:dyDescent="0.25">
@@ -16189,10 +16247,10 @@
         <v>411</v>
       </c>
       <c r="B864">
-        <v>41100769</v>
+        <v>41100766</v>
       </c>
       <c r="C864" t="s">
-        <v>57</v>
+        <v>483</v>
       </c>
     </row>
     <row r="865" spans="1:3" x14ac:dyDescent="0.25">
@@ -16200,10 +16258,10 @@
         <v>411</v>
       </c>
       <c r="B865">
-        <v>41100770</v>
+        <v>41100767</v>
       </c>
       <c r="C865" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="866" spans="1:3" x14ac:dyDescent="0.25">
@@ -16211,10 +16269,10 @@
         <v>411</v>
       </c>
       <c r="B866">
-        <v>41100771</v>
+        <v>41100768</v>
       </c>
       <c r="C866" t="s">
-        <v>486</v>
+        <v>29</v>
       </c>
     </row>
     <row r="867" spans="1:3" x14ac:dyDescent="0.25">
@@ -16222,10 +16280,10 @@
         <v>411</v>
       </c>
       <c r="B867">
-        <v>41100772</v>
+        <v>41100769</v>
       </c>
       <c r="C867" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
     </row>
     <row r="868" spans="1:3" x14ac:dyDescent="0.25">
@@ -16233,10 +16291,10 @@
         <v>411</v>
       </c>
       <c r="B868">
-        <v>41100773</v>
+        <v>41100770</v>
       </c>
       <c r="C868" t="s">
-        <v>91</v>
+        <v>485</v>
       </c>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.25">
@@ -16244,10 +16302,10 @@
         <v>411</v>
       </c>
       <c r="B869">
-        <v>41100774</v>
+        <v>41100771</v>
       </c>
       <c r="C869" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="870" spans="1:3" x14ac:dyDescent="0.25">
@@ -16255,10 +16313,10 @@
         <v>411</v>
       </c>
       <c r="B870">
-        <v>41100775</v>
+        <v>41100772</v>
       </c>
       <c r="C870" t="s">
-        <v>488</v>
+        <v>84</v>
       </c>
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.25">
@@ -16266,10 +16324,10 @@
         <v>411</v>
       </c>
       <c r="B871">
-        <v>41100776</v>
+        <v>41100773</v>
       </c>
       <c r="C871" t="s">
-        <v>489</v>
+        <v>91</v>
       </c>
     </row>
     <row r="872" spans="1:3" x14ac:dyDescent="0.25">
@@ -16277,10 +16335,10 @@
         <v>411</v>
       </c>
       <c r="B872">
-        <v>41100777</v>
+        <v>41100774</v>
       </c>
       <c r="C872" t="s">
-        <v>731</v>
+        <v>487</v>
       </c>
     </row>
     <row r="873" spans="1:3" x14ac:dyDescent="0.25">
@@ -16288,10 +16346,10 @@
         <v>411</v>
       </c>
       <c r="B873">
-        <v>411008</v>
+        <v>41100775</v>
       </c>
       <c r="C873" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="874" spans="1:3" x14ac:dyDescent="0.25">
@@ -16299,43 +16357,43 @@
         <v>411</v>
       </c>
       <c r="B874">
-        <v>411009</v>
+        <v>41100776</v>
       </c>
       <c r="C874" t="s">
-        <v>753</v>
+        <v>489</v>
       </c>
     </row>
     <row r="875" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A875">
         <v>411</v>
       </c>
-      <c r="B875" t="s">
-        <v>491</v>
+      <c r="B875">
+        <v>41100777</v>
       </c>
       <c r="C875" t="s">
-        <v>492</v>
+        <v>731</v>
       </c>
     </row>
     <row r="876" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A876">
         <v>411</v>
       </c>
-      <c r="B876" t="s">
-        <v>493</v>
+      <c r="B876">
+        <v>411008</v>
       </c>
       <c r="C876" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="877" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A877">
         <v>411</v>
       </c>
-      <c r="B877" t="s">
-        <v>495</v>
+      <c r="B877">
+        <v>411009</v>
       </c>
       <c r="C877" t="s">
-        <v>496</v>
+        <v>753</v>
       </c>
     </row>
     <row r="878" spans="1:3" x14ac:dyDescent="0.25">
@@ -16343,10 +16401,10 @@
         <v>411</v>
       </c>
       <c r="B878" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C878" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
     </row>
     <row r="879" spans="1:3" x14ac:dyDescent="0.25">
@@ -16354,10 +16412,10 @@
         <v>411</v>
       </c>
       <c r="B879" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="C879" t="s">
-        <v>155</v>
+        <v>494</v>
       </c>
     </row>
     <row r="880" spans="1:3" x14ac:dyDescent="0.25">
@@ -16365,10 +16423,10 @@
         <v>411</v>
       </c>
       <c r="B880" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="C880" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
     </row>
     <row r="881" spans="1:3" x14ac:dyDescent="0.25">
@@ -16376,10 +16434,10 @@
         <v>411</v>
       </c>
       <c r="B881" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="C881" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.25">
@@ -16387,10 +16445,10 @@
         <v>411</v>
       </c>
       <c r="B882" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C882" t="s">
-        <v>505</v>
+        <v>155</v>
       </c>
     </row>
     <row r="883" spans="1:3" x14ac:dyDescent="0.25">
@@ -16398,10 +16456,10 @@
         <v>411</v>
       </c>
       <c r="B883" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="C883" t="s">
-        <v>152</v>
+        <v>501</v>
       </c>
     </row>
     <row r="884" spans="1:3" x14ac:dyDescent="0.25">
@@ -16409,10 +16467,10 @@
         <v>411</v>
       </c>
       <c r="B884" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C884" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="885" spans="1:3" x14ac:dyDescent="0.25">
@@ -16420,10 +16478,10 @@
         <v>411</v>
       </c>
       <c r="B885" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C885" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
     </row>
     <row r="886" spans="1:3" x14ac:dyDescent="0.25">
@@ -16431,10 +16489,10 @@
         <v>411</v>
       </c>
       <c r="B886" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="C886" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="887" spans="1:3" x14ac:dyDescent="0.25">
@@ -16442,10 +16500,10 @@
         <v>411</v>
       </c>
       <c r="B887" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C887" t="s">
-        <v>157</v>
+        <v>508</v>
       </c>
     </row>
     <row r="888" spans="1:3" x14ac:dyDescent="0.25">
@@ -16453,10 +16511,10 @@
         <v>411</v>
       </c>
       <c r="B888" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C888" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="889" spans="1:3" x14ac:dyDescent="0.25">
@@ -16464,43 +16522,43 @@
         <v>411</v>
       </c>
       <c r="B889" t="s">
-        <v>754</v>
+        <v>511</v>
       </c>
       <c r="C889" t="s">
-        <v>756</v>
+        <v>156</v>
       </c>
     </row>
     <row r="890" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A890">
         <v>411</v>
       </c>
-      <c r="B890">
-        <v>41100006</v>
+      <c r="B890" t="s">
+        <v>512</v>
       </c>
       <c r="C890" t="s">
-        <v>757</v>
+        <v>157</v>
       </c>
     </row>
     <row r="891" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A891">
         <v>411</v>
       </c>
-      <c r="B891">
-        <v>41100005</v>
+      <c r="B891" t="s">
+        <v>513</v>
       </c>
       <c r="C891" t="s">
-        <v>758</v>
+        <v>514</v>
       </c>
     </row>
     <row r="892" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A892">
         <v>411</v>
       </c>
-      <c r="B892">
-        <v>41100011</v>
+      <c r="B892" t="s">
+        <v>754</v>
       </c>
       <c r="C892" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.25">
@@ -16508,14 +16566,83 @@
         <v>411</v>
       </c>
       <c r="B893">
+        <v>41100006</v>
+      </c>
+      <c r="C893" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="894" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A894">
+        <v>411</v>
+      </c>
+      <c r="B894">
+        <v>41100005</v>
+      </c>
+      <c r="C894" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="895" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A895">
+        <v>411</v>
+      </c>
+      <c r="B895">
+        <v>41100011</v>
+      </c>
+      <c r="C895" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="896" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A896">
+        <v>411</v>
+      </c>
+      <c r="B896">
         <v>41100012</v>
       </c>
-      <c r="C893" t="s">
+      <c r="C896" t="s">
         <v>760</v>
       </c>
     </row>
+    <row r="897" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A897">
+        <v>411</v>
+      </c>
+      <c r="B897">
+        <v>41100009</v>
+      </c>
+      <c r="C897" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="898" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A898">
+        <v>411</v>
+      </c>
+      <c r="B898">
+        <v>41100007</v>
+      </c>
+      <c r="C898" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="899" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A899">
+        <v>411</v>
+      </c>
+      <c r="B899">
+        <v>41100008</v>
+      </c>
+      <c r="C899" t="s">
+        <v>766</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B889 A1 B892:B1048576">
+  <conditionalFormatting sqref="B895:B896 B2:B384 A1 B900:B1048576 B388:B892">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B385 B387:B896 B898:B1048576 C897">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
